--- a/src/scores_all.xlsx
+++ b/src/scores_all.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q862"/>
+  <dimension ref="A1:Q863"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -923,7 +923,7 @@
         <v>4</v>
       </c>
       <c r="G8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
         <v>3</v>
@@ -932,10 +932,10 @@
         <v>4</v>
       </c>
       <c r="J8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L8" t="b">
         <v>0</v>
@@ -989,7 +989,7 @@
         <v>4</v>
       </c>
       <c r="H9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I9" t="n">
         <v>4</v>
@@ -998,7 +998,7 @@
         <v>4</v>
       </c>
       <c r="K9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L9" t="b">
         <v>0</v>
@@ -1241,7 +1241,7 @@
         <v>3</v>
       </c>
       <c r="H13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I13" t="n">
         <v>4</v>
@@ -1250,7 +1250,7 @@
         <v>4</v>
       </c>
       <c r="K13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L13" t="b">
         <v>0</v>
@@ -1676,22 +1676,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G20" t="n">
         <v>3</v>
       </c>
       <c r="H20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J20" t="n">
         <v>3</v>
       </c>
       <c r="K20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L20" t="b">
         <v>0</v>
@@ -1751,10 +1751,10 @@
         <v>4</v>
       </c>
       <c r="J21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L21" t="b">
         <v>0</v>
@@ -2435,19 +2435,19 @@
         <v>4</v>
       </c>
       <c r="G32" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H32" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I32" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J32" t="n">
         <v>3</v>
       </c>
       <c r="K32" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="L32" t="b">
         <v>0</v>
@@ -2498,19 +2498,19 @@
         <v>4</v>
       </c>
       <c r="G33" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H33" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I33" t="n">
         <v>4</v>
       </c>
       <c r="J33" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K33" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="L33" t="b">
         <v>0</v>
@@ -3191,7 +3191,7 @@
         <v>4</v>
       </c>
       <c r="G44" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H44" t="n">
         <v>4</v>
@@ -3203,7 +3203,7 @@
         <v>3</v>
       </c>
       <c r="K44" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L44" t="b">
         <v>0</v>
@@ -3632,7 +3632,7 @@
         <v>4</v>
       </c>
       <c r="G51" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H51" t="n">
         <v>4</v>
@@ -3644,7 +3644,7 @@
         <v>4</v>
       </c>
       <c r="K51" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L51" t="b">
         <v>0</v>
@@ -3824,7 +3824,7 @@
         <v>3</v>
       </c>
       <c r="H54" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I54" t="n">
         <v>4</v>
@@ -3833,7 +3833,7 @@
         <v>4</v>
       </c>
       <c r="K54" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L54" t="b">
         <v>0</v>
@@ -3944,7 +3944,7 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G56" t="n">
         <v>3</v>
@@ -3953,13 +3953,13 @@
         <v>3</v>
       </c>
       <c r="I56" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J56" t="n">
         <v>3</v>
       </c>
       <c r="K56" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L56" t="b">
         <v>0</v>
@@ -4007,13 +4007,13 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G57" t="n">
         <v>3</v>
       </c>
       <c r="H57" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I57" t="n">
         <v>3</v>
@@ -4022,7 +4022,7 @@
         <v>3</v>
       </c>
       <c r="K57" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L57" t="b">
         <v>0</v>
@@ -4076,7 +4076,7 @@
         <v>4</v>
       </c>
       <c r="H58" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I58" t="n">
         <v>4</v>
@@ -4085,7 +4085,7 @@
         <v>4</v>
       </c>
       <c r="K58" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L58" t="b">
         <v>0</v>
@@ -4706,7 +4706,7 @@
         <v>3</v>
       </c>
       <c r="H68" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I68" t="n">
         <v>4</v>
@@ -4715,7 +4715,7 @@
         <v>4</v>
       </c>
       <c r="K68" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L68" t="b">
         <v>0</v>
@@ -4772,13 +4772,13 @@
         <v>4</v>
       </c>
       <c r="I69" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J69" t="n">
         <v>4</v>
       </c>
       <c r="K69" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L69" t="b">
         <v>0</v>
@@ -5333,10 +5333,10 @@
         <v>4</v>
       </c>
       <c r="G78" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H78" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I78" t="n">
         <v>4</v>
@@ -5774,7 +5774,7 @@
         <v>4</v>
       </c>
       <c r="G85" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H85" t="n">
         <v>4</v>
@@ -5786,7 +5786,7 @@
         <v>4</v>
       </c>
       <c r="K85" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L85" t="b">
         <v>0</v>
@@ -6215,19 +6215,19 @@
         <v>4</v>
       </c>
       <c r="G92" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H92" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I92" t="n">
         <v>4</v>
       </c>
       <c r="J92" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K92" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="L92" t="b">
         <v>0</v>
@@ -6278,19 +6278,19 @@
         <v>4</v>
       </c>
       <c r="G93" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H93" t="n">
         <v>4</v>
       </c>
       <c r="I93" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J93" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K93" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L93" t="b">
         <v>0</v>
@@ -6974,7 +6974,7 @@
         <v>3</v>
       </c>
       <c r="H104" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I104" t="n">
         <v>3</v>
@@ -6983,7 +6983,7 @@
         <v>3</v>
       </c>
       <c r="K104" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L104" t="b">
         <v>0</v>
@@ -7034,7 +7034,7 @@
         <v>4</v>
       </c>
       <c r="G105" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H105" t="n">
         <v>3</v>
@@ -7043,10 +7043,10 @@
         <v>4</v>
       </c>
       <c r="J105" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K105" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L105" t="b">
         <v>0</v>
@@ -7727,19 +7727,19 @@
         <v>4</v>
       </c>
       <c r="G116" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H116" t="n">
         <v>4</v>
       </c>
       <c r="I116" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J116" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K116" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L116" t="b">
         <v>0</v>
@@ -7799,10 +7799,10 @@
         <v>4</v>
       </c>
       <c r="J117" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K117" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L117" t="b">
         <v>0</v>
@@ -8171,7 +8171,7 @@
         <v>3</v>
       </c>
       <c r="H123" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I123" t="n">
         <v>4</v>
@@ -8180,7 +8180,7 @@
         <v>4</v>
       </c>
       <c r="K123" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L123" t="b">
         <v>0</v>
@@ -8798,10 +8798,10 @@
         <v>4</v>
       </c>
       <c r="G133" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H133" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I133" t="n">
         <v>4</v>
@@ -9245,13 +9245,13 @@
         <v>4</v>
       </c>
       <c r="I140" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J140" t="n">
         <v>3</v>
       </c>
       <c r="K140" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L140" t="b">
         <v>0</v>
@@ -9305,16 +9305,16 @@
         <v>4</v>
       </c>
       <c r="H141" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I141" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J141" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K141" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L141" t="b">
         <v>0</v>
@@ -9869,10 +9869,10 @@
         <v>4</v>
       </c>
       <c r="G150" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H150" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I150" t="n">
         <v>4</v>
@@ -9881,7 +9881,7 @@
         <v>4</v>
       </c>
       <c r="K150" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L150" t="b">
         <v>0</v>
@@ -10067,10 +10067,10 @@
         <v>4</v>
       </c>
       <c r="J153" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K153" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L153" t="b">
         <v>0</v>
@@ -10124,7 +10124,7 @@
         <v>4</v>
       </c>
       <c r="H154" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I154" t="n">
         <v>4</v>
@@ -10133,7 +10133,7 @@
         <v>4</v>
       </c>
       <c r="K154" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L154" t="b">
         <v>0</v>
@@ -10310,7 +10310,7 @@
         <v>4</v>
       </c>
       <c r="G157" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H157" t="n">
         <v>4</v>
@@ -10322,7 +10322,7 @@
         <v>4</v>
       </c>
       <c r="K157" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L157" t="b">
         <v>0</v>
@@ -10757,13 +10757,13 @@
         <v>3</v>
       </c>
       <c r="I164" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J164" t="n">
         <v>3</v>
       </c>
       <c r="K164" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L164" t="b">
         <v>0</v>
@@ -11510,16 +11510,16 @@
         <v>3</v>
       </c>
       <c r="H176" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I176" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J176" t="n">
         <v>3</v>
       </c>
       <c r="K176" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L176" t="b">
         <v>0</v>
@@ -11567,13 +11567,13 @@
         </is>
       </c>
       <c r="F177" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G177" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H177" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I177" t="n">
         <v>4</v>
@@ -11582,7 +11582,7 @@
         <v>3</v>
       </c>
       <c r="K177" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="L177" t="b">
         <v>0</v>
@@ -12269,13 +12269,13 @@
         <v>4</v>
       </c>
       <c r="I188" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J188" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K188" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L188" t="b">
         <v>0</v>
@@ -12707,7 +12707,7 @@
         <v>4</v>
       </c>
       <c r="H195" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I195" t="n">
         <v>4</v>
@@ -12716,7 +12716,7 @@
         <v>4</v>
       </c>
       <c r="K195" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L195" t="b">
         <v>0</v>
@@ -13079,13 +13079,13 @@
         </is>
       </c>
       <c r="F201" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G201" t="n">
         <v>3</v>
       </c>
       <c r="H201" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I201" t="n">
         <v>3</v>
@@ -13094,7 +13094,7 @@
         <v>3</v>
       </c>
       <c r="K201" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L201" t="b">
         <v>0</v>
@@ -13145,7 +13145,7 @@
         <v>4</v>
       </c>
       <c r="G202" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H202" t="n">
         <v>3</v>
@@ -13157,7 +13157,7 @@
         <v>4</v>
       </c>
       <c r="K202" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L202" t="b">
         <v>0</v>
@@ -13334,10 +13334,10 @@
         <v>4</v>
       </c>
       <c r="G205" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H205" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I205" t="n">
         <v>4</v>
@@ -13346,7 +13346,7 @@
         <v>4</v>
       </c>
       <c r="K205" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L205" t="b">
         <v>0</v>
@@ -13775,7 +13775,7 @@
         <v>4</v>
       </c>
       <c r="G212" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H212" t="n">
         <v>4</v>
@@ -13787,7 +13787,7 @@
         <v>4</v>
       </c>
       <c r="K212" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L212" t="b">
         <v>0</v>
@@ -13835,22 +13835,22 @@
         </is>
       </c>
       <c r="F213" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G213" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H213" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I213" t="n">
         <v>4</v>
       </c>
       <c r="J213" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K213" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="L213" t="b">
         <v>0</v>
@@ -14408,7 +14408,7 @@
         <v>4</v>
       </c>
       <c r="H222" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I222" t="n">
         <v>4</v>
@@ -14417,7 +14417,7 @@
         <v>4</v>
       </c>
       <c r="K222" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L222" t="b">
         <v>0</v>
@@ -14528,22 +14528,22 @@
         </is>
       </c>
       <c r="F224" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G224" t="n">
         <v>3</v>
       </c>
       <c r="H224" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I224" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J224" t="n">
         <v>3</v>
       </c>
       <c r="K224" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="L224" t="b">
         <v>0</v>
@@ -14597,7 +14597,7 @@
         <v>4</v>
       </c>
       <c r="H225" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I225" t="n">
         <v>4</v>
@@ -14606,7 +14606,7 @@
         <v>4</v>
       </c>
       <c r="K225" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L225" t="b">
         <v>0</v>
@@ -14660,7 +14660,7 @@
         <v>4</v>
       </c>
       <c r="H226" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I226" t="n">
         <v>4</v>
@@ -14669,7 +14669,7 @@
         <v>4</v>
       </c>
       <c r="K226" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L226" t="b">
         <v>0</v>
@@ -14846,10 +14846,10 @@
         <v>4</v>
       </c>
       <c r="G229" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H229" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I229" t="n">
         <v>4</v>
@@ -14858,7 +14858,7 @@
         <v>4</v>
       </c>
       <c r="K229" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L229" t="b">
         <v>0</v>
@@ -15293,13 +15293,13 @@
         <v>4</v>
       </c>
       <c r="I236" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J236" t="n">
         <v>3</v>
       </c>
       <c r="K236" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L236" t="b">
         <v>0</v>
@@ -15356,13 +15356,13 @@
         <v>4</v>
       </c>
       <c r="I237" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J237" t="n">
         <v>4</v>
       </c>
       <c r="K237" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L237" t="b">
         <v>0</v>
@@ -16799,7 +16799,7 @@
         <v>4</v>
       </c>
       <c r="G260" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H260" t="n">
         <v>4</v>
@@ -16811,7 +16811,7 @@
         <v>3</v>
       </c>
       <c r="K260" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L260" t="b">
         <v>0</v>
@@ -17240,10 +17240,10 @@
         <v>4</v>
       </c>
       <c r="G267" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H267" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I267" t="n">
         <v>4</v>
@@ -17252,7 +17252,7 @@
         <v>4</v>
       </c>
       <c r="K267" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L267" t="b">
         <v>0</v>
@@ -17552,7 +17552,7 @@
         </is>
       </c>
       <c r="F272" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G272" t="n">
         <v>3</v>
@@ -17561,13 +17561,13 @@
         <v>3</v>
       </c>
       <c r="I272" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J272" t="n">
         <v>3</v>
       </c>
       <c r="K272" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L272" t="b">
         <v>0</v>
@@ -17618,19 +17618,19 @@
         <v>4</v>
       </c>
       <c r="G273" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H273" t="n">
         <v>3</v>
       </c>
       <c r="I273" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J273" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K273" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="L273" t="b">
         <v>0</v>
@@ -18320,10 +18320,10 @@
         <v>3</v>
       </c>
       <c r="J284" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K284" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L284" t="b">
         <v>0</v>
@@ -19073,13 +19073,13 @@
         <v>3</v>
       </c>
       <c r="I296" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J296" t="n">
         <v>3</v>
       </c>
       <c r="K296" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L296" t="b">
         <v>0</v>
@@ -19133,7 +19133,7 @@
         <v>4</v>
       </c>
       <c r="H297" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I297" t="n">
         <v>4</v>
@@ -19142,7 +19142,7 @@
         <v>4</v>
       </c>
       <c r="K297" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L297" t="b">
         <v>0</v>
@@ -19382,10 +19382,10 @@
         <v>4</v>
       </c>
       <c r="G301" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H301" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I301" t="n">
         <v>4</v>
@@ -19394,7 +19394,7 @@
         <v>4</v>
       </c>
       <c r="K301" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L301" t="b">
         <v>0</v>
@@ -19823,7 +19823,7 @@
         <v>4</v>
       </c>
       <c r="G308" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H308" t="n">
         <v>4</v>
@@ -19832,10 +19832,10 @@
         <v>4</v>
       </c>
       <c r="J308" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K308" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L308" t="b">
         <v>0</v>
@@ -20582,7 +20582,7 @@
         <v>3</v>
       </c>
       <c r="H320" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I320" t="n">
         <v>3</v>
@@ -20591,7 +20591,7 @@
         <v>3</v>
       </c>
       <c r="K320" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L320" t="b">
         <v>0</v>
@@ -20651,10 +20651,10 @@
         <v>4</v>
       </c>
       <c r="J321" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K321" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L321" t="b">
         <v>0</v>
@@ -21332,7 +21332,7 @@
         </is>
       </c>
       <c r="F332" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G332" t="n">
         <v>3</v>
@@ -21341,19 +21341,19 @@
         <v>4</v>
       </c>
       <c r="I332" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J332" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K332" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="L332" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M332" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N332" t="b">
         <v>0</v>
@@ -21782,13 +21782,13 @@
         <v>4</v>
       </c>
       <c r="I339" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J339" t="n">
         <v>4</v>
       </c>
       <c r="K339" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L339" t="b">
         <v>0</v>
@@ -22151,22 +22151,22 @@
         </is>
       </c>
       <c r="F345" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G345" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H345" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I345" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J345" t="n">
         <v>3</v>
       </c>
       <c r="K345" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="L345" t="b">
         <v>0</v>
@@ -22220,7 +22220,7 @@
         <v>4</v>
       </c>
       <c r="H346" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I346" t="n">
         <v>4</v>
@@ -22229,7 +22229,7 @@
         <v>4</v>
       </c>
       <c r="K346" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L346" t="b">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         <v>4</v>
       </c>
       <c r="G349" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H349" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I349" t="n">
         <v>4</v>
@@ -22853,13 +22853,13 @@
         <v>4</v>
       </c>
       <c r="I356" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J356" t="n">
         <v>3</v>
       </c>
       <c r="K356" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L356" t="b">
         <v>0</v>
@@ -22910,7 +22910,7 @@
         <v>4</v>
       </c>
       <c r="G357" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H357" t="n">
         <v>4</v>
@@ -22919,10 +22919,10 @@
         <v>4</v>
       </c>
       <c r="J357" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K357" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L357" t="b">
         <v>0</v>
@@ -23291,7 +23291,7 @@
         <v>4</v>
       </c>
       <c r="H363" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I363" t="n">
         <v>4</v>
@@ -23300,7 +23300,7 @@
         <v>4</v>
       </c>
       <c r="K363" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L363" t="b">
         <v>0</v>
@@ -23609,13 +23609,13 @@
         <v>3</v>
       </c>
       <c r="I368" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J368" t="n">
         <v>3</v>
       </c>
       <c r="K368" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L368" t="b">
         <v>0</v>
@@ -24368,10 +24368,10 @@
         <v>4</v>
       </c>
       <c r="J380" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K380" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L380" t="b">
         <v>0</v>
@@ -25115,7 +25115,7 @@
         <v>4</v>
       </c>
       <c r="G392" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H392" t="n">
         <v>4</v>
@@ -25124,10 +25124,10 @@
         <v>4</v>
       </c>
       <c r="J392" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K392" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L392" t="b">
         <v>0</v>
@@ -25877,13 +25877,13 @@
         <v>4</v>
       </c>
       <c r="I404" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J404" t="n">
         <v>3</v>
       </c>
       <c r="K404" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L404" t="b">
         <v>0</v>
@@ -26318,13 +26318,13 @@
         <v>4</v>
       </c>
       <c r="I411" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J411" t="n">
         <v>4</v>
       </c>
       <c r="K411" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L411" t="b">
         <v>0</v>
@@ -26501,7 +26501,7 @@
         <v>4</v>
       </c>
       <c r="G414" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H414" t="n">
         <v>4</v>
@@ -26513,7 +26513,7 @@
         <v>4</v>
       </c>
       <c r="K414" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L414" t="b">
         <v>0</v>
@@ -26624,7 +26624,7 @@
         </is>
       </c>
       <c r="F416" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G416" t="n">
         <v>3</v>
@@ -26639,7 +26639,7 @@
         <v>3</v>
       </c>
       <c r="K416" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L416" t="b">
         <v>0</v>
@@ -26693,7 +26693,7 @@
         <v>3</v>
       </c>
       <c r="H417" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I417" t="n">
         <v>3</v>
@@ -26702,7 +26702,7 @@
         <v>3</v>
       </c>
       <c r="K417" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L417" t="b">
         <v>0</v>
@@ -26756,7 +26756,7 @@
         <v>4</v>
       </c>
       <c r="H418" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I418" t="n">
         <v>4</v>
@@ -26765,7 +26765,7 @@
         <v>4</v>
       </c>
       <c r="K418" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L418" t="b">
         <v>0</v>
@@ -27386,16 +27386,16 @@
         <v>3</v>
       </c>
       <c r="H428" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I428" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J428" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K428" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L428" t="b">
         <v>0</v>
@@ -27449,16 +27449,16 @@
         <v>3</v>
       </c>
       <c r="H429" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I429" t="n">
         <v>4</v>
       </c>
       <c r="J429" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K429" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L429" t="b">
         <v>0</v>
@@ -28016,16 +28016,16 @@
         <v>3</v>
       </c>
       <c r="H438" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I438" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J438" t="n">
         <v>4</v>
       </c>
       <c r="K438" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L438" t="b">
         <v>0</v>
@@ -28136,7 +28136,7 @@
         </is>
       </c>
       <c r="F440" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G440" t="n">
         <v>3</v>
@@ -28151,7 +28151,7 @@
         <v>3</v>
       </c>
       <c r="K440" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L440" t="b">
         <v>0</v>
@@ -28199,22 +28199,22 @@
         </is>
       </c>
       <c r="F441" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G441" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H441" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I441" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J441" t="n">
         <v>3</v>
       </c>
       <c r="K441" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="L441" t="b">
         <v>0</v>
@@ -28898,13 +28898,13 @@
         <v>3</v>
       </c>
       <c r="H452" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I452" t="n">
         <v>4</v>
       </c>
       <c r="J452" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K452" t="n">
         <v>18</v>
@@ -28967,10 +28967,10 @@
         <v>4</v>
       </c>
       <c r="J453" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K453" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L453" t="b">
         <v>0</v>
@@ -29654,7 +29654,7 @@
         <v>3</v>
       </c>
       <c r="H464" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I464" t="n">
         <v>3</v>
@@ -29663,7 +29663,7 @@
         <v>3</v>
       </c>
       <c r="K464" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L464" t="b">
         <v>0</v>
@@ -29723,10 +29723,10 @@
         <v>4</v>
       </c>
       <c r="J465" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K465" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L465" t="b">
         <v>0</v>
@@ -29972,13 +29972,13 @@
         <v>4</v>
       </c>
       <c r="I469" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J469" t="n">
         <v>4</v>
       </c>
       <c r="K469" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L469" t="b">
         <v>0</v>
@@ -30413,13 +30413,13 @@
         <v>4</v>
       </c>
       <c r="I476" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J476" t="n">
         <v>3</v>
       </c>
       <c r="K476" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L476" t="b">
         <v>0</v>
@@ -30476,13 +30476,13 @@
         <v>4</v>
       </c>
       <c r="I477" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J477" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K477" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L477" t="b">
         <v>0</v>
@@ -30848,7 +30848,7 @@
         <v>4</v>
       </c>
       <c r="G483" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H483" t="n">
         <v>3</v>
@@ -30860,7 +30860,7 @@
         <v>4</v>
       </c>
       <c r="K483" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L483" t="b">
         <v>0</v>
@@ -31037,19 +31037,19 @@
         <v>4</v>
       </c>
       <c r="G486" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H486" t="n">
         <v>3</v>
       </c>
       <c r="I486" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J486" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K486" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="L486" t="b">
         <v>0</v>
@@ -31160,7 +31160,7 @@
         </is>
       </c>
       <c r="F488" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G488" t="n">
         <v>3</v>
@@ -31175,7 +31175,7 @@
         <v>3</v>
       </c>
       <c r="K488" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L488" t="b">
         <v>0</v>
@@ -31235,10 +31235,10 @@
         <v>3</v>
       </c>
       <c r="J489" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K489" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L489" t="b">
         <v>0</v>
@@ -31478,19 +31478,19 @@
         <v>4</v>
       </c>
       <c r="G493" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H493" t="n">
         <v>3</v>
       </c>
       <c r="I493" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J493" t="n">
         <v>4</v>
       </c>
       <c r="K493" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L493" t="b">
         <v>0</v>
@@ -31922,16 +31922,16 @@
         <v>3</v>
       </c>
       <c r="H500" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I500" t="n">
         <v>4</v>
       </c>
       <c r="J500" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K500" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L500" t="b">
         <v>0</v>
@@ -31979,22 +31979,22 @@
         </is>
       </c>
       <c r="F501" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G501" t="n">
         <v>3</v>
       </c>
       <c r="H501" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I501" t="n">
         <v>4</v>
       </c>
       <c r="J501" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K501" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="L501" t="b">
         <v>0</v>
@@ -32681,13 +32681,13 @@
         <v>3</v>
       </c>
       <c r="I512" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J512" t="n">
         <v>3</v>
       </c>
       <c r="K512" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L512" t="b">
         <v>0</v>
@@ -32741,13 +32741,13 @@
         <v>4</v>
       </c>
       <c r="H513" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I513" t="n">
         <v>4</v>
       </c>
       <c r="J513" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K513" t="n">
         <v>19</v>
@@ -32804,7 +32804,7 @@
         <v>4</v>
       </c>
       <c r="H514" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I514" t="n">
         <v>4</v>
@@ -32813,7 +32813,7 @@
         <v>4</v>
       </c>
       <c r="K514" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L514" t="b">
         <v>0</v>
@@ -32990,7 +32990,7 @@
         <v>4</v>
       </c>
       <c r="G517" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H517" t="n">
         <v>4</v>
@@ -33002,7 +33002,7 @@
         <v>4</v>
       </c>
       <c r="K517" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L517" t="b">
         <v>0</v>
@@ -33428,7 +33428,7 @@
         </is>
       </c>
       <c r="F524" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G524" t="n">
         <v>3</v>
@@ -33437,13 +33437,13 @@
         <v>4</v>
       </c>
       <c r="I524" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J524" t="n">
         <v>3</v>
       </c>
       <c r="K524" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L524" t="b">
         <v>0</v>
@@ -34187,13 +34187,13 @@
         <v>4</v>
       </c>
       <c r="G536" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H536" t="n">
         <v>4</v>
       </c>
       <c r="I536" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J536" t="n">
         <v>3</v>
@@ -35015,10 +35015,10 @@
         <v>4</v>
       </c>
       <c r="J549" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K549" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L549" t="b">
         <v>0</v>
@@ -35384,7 +35384,7 @@
         <v>4</v>
       </c>
       <c r="G555" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H555" t="n">
         <v>4</v>
@@ -35396,7 +35396,7 @@
         <v>4</v>
       </c>
       <c r="K555" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L555" t="b">
         <v>0</v>
@@ -35573,19 +35573,19 @@
         <v>4</v>
       </c>
       <c r="G558" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H558" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I558" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J558" t="n">
         <v>4</v>
       </c>
       <c r="K558" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="L558" t="b">
         <v>0</v>
@@ -35696,22 +35696,22 @@
         </is>
       </c>
       <c r="F560" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G560" t="n">
         <v>3</v>
       </c>
       <c r="H560" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I560" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J560" t="n">
         <v>3</v>
       </c>
       <c r="K560" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="L560" t="b">
         <v>0</v>
@@ -35759,22 +35759,22 @@
         </is>
       </c>
       <c r="F561" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G561" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H561" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I561" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J561" t="n">
         <v>3</v>
       </c>
       <c r="K561" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L561" t="b">
         <v>0</v>
@@ -35828,7 +35828,7 @@
         <v>4</v>
       </c>
       <c r="H562" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I562" t="n">
         <v>4</v>
@@ -35837,7 +35837,7 @@
         <v>4</v>
       </c>
       <c r="K562" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L562" t="b">
         <v>0</v>
@@ -36527,10 +36527,10 @@
         <v>4</v>
       </c>
       <c r="J573" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K573" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L573" t="b">
         <v>0</v>
@@ -36896,10 +36896,10 @@
         <v>4</v>
       </c>
       <c r="G579" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H579" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I579" t="n">
         <v>4</v>
@@ -37085,10 +37085,10 @@
         <v>4</v>
       </c>
       <c r="G582" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H582" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I582" t="n">
         <v>4</v>
@@ -37214,7 +37214,7 @@
         <v>3</v>
       </c>
       <c r="H584" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I584" t="n">
         <v>3</v>
@@ -37223,7 +37223,7 @@
         <v>3</v>
       </c>
       <c r="K584" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L584" t="b">
         <v>0</v>
@@ -37271,22 +37271,22 @@
         </is>
       </c>
       <c r="F585" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G585" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H585" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I585" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J585" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K585" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L585" t="b">
         <v>0</v>
@@ -37340,7 +37340,7 @@
         <v>4</v>
       </c>
       <c r="H586" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I586" t="n">
         <v>4</v>
@@ -37349,7 +37349,7 @@
         <v>4</v>
       </c>
       <c r="K586" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L586" t="b">
         <v>0</v>
@@ -37529,7 +37529,7 @@
         <v>4</v>
       </c>
       <c r="H589" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I589" t="n">
         <v>4</v>
@@ -37538,7 +37538,7 @@
         <v>4</v>
       </c>
       <c r="K589" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L589" t="b">
         <v>0</v>
@@ -37973,13 +37973,13 @@
         <v>4</v>
       </c>
       <c r="I596" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J596" t="n">
         <v>3</v>
       </c>
       <c r="K596" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L596" t="b">
         <v>0</v>
@@ -38723,19 +38723,19 @@
         <v>4</v>
       </c>
       <c r="G608" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H608" t="n">
         <v>4</v>
       </c>
       <c r="I608" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J608" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K608" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="L608" t="b">
         <v>0</v>
@@ -39479,13 +39479,13 @@
         <v>4</v>
       </c>
       <c r="G620" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H620" t="n">
         <v>4</v>
       </c>
       <c r="I620" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J620" t="n">
         <v>3</v>
@@ -39551,10 +39551,10 @@
         <v>4</v>
       </c>
       <c r="J621" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K621" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L621" t="b">
         <v>0</v>
@@ -40232,7 +40232,7 @@
         </is>
       </c>
       <c r="F632" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G632" t="n">
         <v>3</v>
@@ -40247,7 +40247,7 @@
         <v>3</v>
       </c>
       <c r="K632" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L632" t="b">
         <v>0</v>
@@ -40295,22 +40295,22 @@
         </is>
       </c>
       <c r="F633" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G633" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H633" t="n">
         <v>2</v>
       </c>
       <c r="I633" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J633" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K633" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="L633" t="b">
         <v>0</v>
@@ -40364,7 +40364,7 @@
         <v>4</v>
       </c>
       <c r="H634" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I634" t="n">
         <v>4</v>
@@ -40373,7 +40373,7 @@
         <v>4</v>
       </c>
       <c r="K634" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L634" t="b">
         <v>0</v>
@@ -40556,13 +40556,13 @@
         <v>4</v>
       </c>
       <c r="I637" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J637" t="n">
         <v>4</v>
       </c>
       <c r="K637" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L637" t="b">
         <v>0</v>
@@ -41054,10 +41054,10 @@
         <v>4</v>
       </c>
       <c r="G645" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H645" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I645" t="n">
         <v>4</v>
@@ -41753,13 +41753,13 @@
         <v>3</v>
       </c>
       <c r="I656" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J656" t="n">
         <v>3</v>
       </c>
       <c r="K656" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L656" t="b">
         <v>0</v>
@@ -41810,19 +41810,19 @@
         <v>4</v>
       </c>
       <c r="G657" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H657" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I657" t="n">
         <v>4</v>
       </c>
       <c r="J657" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K657" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="L657" t="b">
         <v>0</v>
@@ -42503,7 +42503,7 @@
         <v>4</v>
       </c>
       <c r="G668" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H668" t="n">
         <v>4</v>
@@ -42515,7 +42515,7 @@
         <v>3</v>
       </c>
       <c r="K668" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L668" t="b">
         <v>0</v>
@@ -43265,13 +43265,13 @@
         <v>4</v>
       </c>
       <c r="I680" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J680" t="n">
         <v>3</v>
       </c>
       <c r="K680" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L680" t="b">
         <v>0</v>
@@ -44087,10 +44087,10 @@
         <v>4</v>
       </c>
       <c r="J693" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K693" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L693" t="b">
         <v>0</v>
@@ -44831,22 +44831,22 @@
         </is>
       </c>
       <c r="F705" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G705" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H705" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I705" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J705" t="n">
         <v>3</v>
       </c>
       <c r="K705" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="L705" t="b">
         <v>0</v>
@@ -45968,10 +45968,10 @@
         <v>4</v>
       </c>
       <c r="G723" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H723" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I723" t="n">
         <v>4</v>
@@ -45980,7 +45980,7 @@
         <v>4</v>
       </c>
       <c r="K723" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L723" t="b">
         <v>0</v>
@@ -46280,22 +46280,22 @@
         </is>
       </c>
       <c r="F728" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G728" t="n">
         <v>3</v>
       </c>
       <c r="H728" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I728" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J728" t="n">
         <v>3</v>
       </c>
       <c r="K728" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="L728" t="b">
         <v>0</v>
@@ -46412,7 +46412,7 @@
         <v>4</v>
       </c>
       <c r="H730" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I730" t="n">
         <v>4</v>
@@ -46421,7 +46421,7 @@
         <v>4</v>
       </c>
       <c r="K730" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L730" t="b">
         <v>0</v>
@@ -47111,10 +47111,10 @@
         <v>4</v>
       </c>
       <c r="J741" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K741" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L741" t="b">
         <v>0</v>
@@ -47795,7 +47795,7 @@
         <v>4</v>
       </c>
       <c r="G752" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H752" t="n">
         <v>4</v>
@@ -47807,7 +47807,7 @@
         <v>3</v>
       </c>
       <c r="K752" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L752" t="b">
         <v>0</v>
@@ -48617,13 +48617,13 @@
         <v>4</v>
       </c>
       <c r="H765" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I765" t="n">
         <v>4</v>
       </c>
       <c r="J765" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K765" t="n">
         <v>19</v>
@@ -48917,49 +48917,49 @@
       </c>
       <c r="D770" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="E770" t="inlineStr">
         <is>
-          <t>chatgpt</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="F770" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G770" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H770" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I770" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J770" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K770" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="L770" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M770" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N770" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O770" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P770" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q770" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="771">
@@ -48985,26 +48985,26 @@
       </c>
       <c r="E771" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="F771" t="n">
         <v>4</v>
       </c>
       <c r="G771" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H771" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I771" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J771" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K771" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="L771" t="b">
         <v>0</v>
@@ -49048,7 +49048,7 @@
       </c>
       <c r="E772" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="F772" t="n">
@@ -49106,31 +49106,31 @@
       </c>
       <c r="D773" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="E773" t="inlineStr">
         <is>
-          <t>chatgpt</t>
+          <t>grok</t>
         </is>
       </c>
       <c r="F773" t="n">
         <v>4</v>
       </c>
       <c r="G773" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H773" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I773" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J773" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K773" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L773" t="b">
         <v>0</v>
@@ -49174,26 +49174,26 @@
       </c>
       <c r="E774" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="F774" t="n">
         <v>4</v>
       </c>
       <c r="G774" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H774" t="n">
         <v>3</v>
       </c>
       <c r="I774" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J774" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K774" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="L774" t="b">
         <v>0</v>
@@ -49237,26 +49237,26 @@
       </c>
       <c r="E775" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="F775" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G775" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H775" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I775" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J775" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K775" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="L775" t="b">
         <v>0</v>
@@ -49295,31 +49295,31 @@
       </c>
       <c r="D776" t="inlineStr">
         <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="E776" t="inlineStr">
+        <is>
           <t>grok</t>
         </is>
       </c>
-      <c r="E776" t="inlineStr">
-        <is>
-          <t>chatgpt</t>
-        </is>
-      </c>
       <c r="F776" t="n">
         <v>4</v>
       </c>
       <c r="G776" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H776" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I776" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J776" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K776" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L776" t="b">
         <v>0</v>
@@ -49363,26 +49363,26 @@
       </c>
       <c r="E777" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="F777" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G777" t="n">
         <v>3</v>
       </c>
       <c r="H777" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I777" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J777" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K777" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="L777" t="b">
         <v>0</v>
@@ -49426,26 +49426,26 @@
       </c>
       <c r="E778" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="F778" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G778" t="n">
         <v>3</v>
       </c>
       <c r="H778" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I778" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J778" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K778" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="L778" t="b">
         <v>0</v>
@@ -49479,17 +49479,17 @@
       </c>
       <c r="C779" t="inlineStr">
         <is>
-          <t>tune</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="D779" t="inlineStr">
         <is>
-          <t>chatgpt</t>
+          <t>grok</t>
         </is>
       </c>
       <c r="E779" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="F779" t="n">
@@ -49552,7 +49552,7 @@
       </c>
       <c r="E780" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="F780" t="n">
@@ -49615,7 +49615,7 @@
       </c>
       <c r="E781" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="F781" t="n">
@@ -49673,19 +49673,19 @@
       </c>
       <c r="D782" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="E782" t="inlineStr">
         <is>
-          <t>chatgpt</t>
+          <t>grok</t>
         </is>
       </c>
       <c r="F782" t="n">
         <v>4</v>
       </c>
       <c r="G782" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H782" t="n">
         <v>4</v>
@@ -49697,7 +49697,7 @@
         <v>4</v>
       </c>
       <c r="K782" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L782" t="b">
         <v>0</v>
@@ -49741,14 +49741,14 @@
       </c>
       <c r="E783" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="F783" t="n">
         <v>4</v>
       </c>
       <c r="G783" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H783" t="n">
         <v>4</v>
@@ -49760,7 +49760,7 @@
         <v>4</v>
       </c>
       <c r="K783" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L783" t="b">
         <v>0</v>
@@ -49804,7 +49804,7 @@
       </c>
       <c r="E784" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="F784" t="n">
@@ -49862,31 +49862,31 @@
       </c>
       <c r="D785" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="E785" t="inlineStr">
         <is>
-          <t>chatgpt</t>
+          <t>grok</t>
         </is>
       </c>
       <c r="F785" t="n">
         <v>4</v>
       </c>
       <c r="G785" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H785" t="n">
         <v>4</v>
       </c>
       <c r="I785" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J785" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K785" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L785" t="b">
         <v>0</v>
@@ -49930,26 +49930,26 @@
       </c>
       <c r="E786" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="F786" t="n">
         <v>4</v>
       </c>
       <c r="G786" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H786" t="n">
         <v>4</v>
       </c>
       <c r="I786" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J786" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K786" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="L786" t="b">
         <v>0</v>
@@ -49993,26 +49993,26 @@
       </c>
       <c r="E787" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="F787" t="n">
         <v>4</v>
       </c>
       <c r="G787" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H787" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I787" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J787" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K787" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="L787" t="b">
         <v>0</v>
@@ -50051,14 +50051,14 @@
       </c>
       <c r="D788" t="inlineStr">
         <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="E788" t="inlineStr">
+        <is>
           <t>grok</t>
         </is>
       </c>
-      <c r="E788" t="inlineStr">
-        <is>
-          <t>chatgpt</t>
-        </is>
-      </c>
       <c r="F788" t="n">
         <v>4</v>
       </c>
@@ -50066,16 +50066,16 @@
         <v>4</v>
       </c>
       <c r="H788" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I788" t="n">
         <v>4</v>
       </c>
       <c r="J788" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K788" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L788" t="b">
         <v>0</v>
@@ -50119,7 +50119,7 @@
       </c>
       <c r="E789" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="F789" t="n">
@@ -50129,16 +50129,16 @@
         <v>4</v>
       </c>
       <c r="H789" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I789" t="n">
         <v>4</v>
       </c>
       <c r="J789" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K789" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L789" t="b">
         <v>0</v>
@@ -50182,7 +50182,7 @@
       </c>
       <c r="E790" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="F790" t="n">
@@ -50225,37 +50225,37 @@
     <row r="791">
       <c r="A791" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p10</t>
         </is>
       </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A3</t>
         </is>
       </c>
       <c r="C791" t="inlineStr">
         <is>
-          <t>generate</t>
+          <t>tune</t>
         </is>
       </c>
       <c r="D791" t="inlineStr">
         <is>
-          <t>chatgpt</t>
+          <t>grok</t>
         </is>
       </c>
       <c r="E791" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="F791" t="n">
         <v>4</v>
       </c>
       <c r="G791" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H791" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I791" t="n">
         <v>4</v>
@@ -50264,7 +50264,7 @@
         <v>4</v>
       </c>
       <c r="K791" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L791" t="b">
         <v>0</v>
@@ -50288,7 +50288,7 @@
     <row r="792">
       <c r="A792" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p12</t>
         </is>
       </c>
       <c r="B792" t="inlineStr">
@@ -50308,7 +50308,7 @@
       </c>
       <c r="E792" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="F792" t="n">
@@ -50318,7 +50318,7 @@
         <v>4</v>
       </c>
       <c r="H792" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I792" t="n">
         <v>4</v>
@@ -50327,7 +50327,7 @@
         <v>4</v>
       </c>
       <c r="K792" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L792" t="b">
         <v>0</v>
@@ -50351,7 +50351,7 @@
     <row r="793">
       <c r="A793" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p12</t>
         </is>
       </c>
       <c r="B793" t="inlineStr">
@@ -50371,7 +50371,7 @@
       </c>
       <c r="E793" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="F793" t="n">
@@ -50414,7 +50414,7 @@
     <row r="794">
       <c r="A794" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p12</t>
         </is>
       </c>
       <c r="B794" t="inlineStr">
@@ -50429,12 +50429,12 @@
       </c>
       <c r="D794" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="E794" t="inlineStr">
         <is>
-          <t>chatgpt</t>
+          <t>grok</t>
         </is>
       </c>
       <c r="F794" t="n">
@@ -50444,16 +50444,16 @@
         <v>4</v>
       </c>
       <c r="H794" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I794" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J794" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K794" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L794" t="b">
         <v>0</v>
@@ -50477,7 +50477,7 @@
     <row r="795">
       <c r="A795" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p12</t>
         </is>
       </c>
       <c r="B795" t="inlineStr">
@@ -50497,26 +50497,26 @@
       </c>
       <c r="E795" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="F795" t="n">
         <v>4</v>
       </c>
       <c r="G795" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H795" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I795" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J795" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K795" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="L795" t="b">
         <v>0</v>
@@ -50540,7 +50540,7 @@
     <row r="796">
       <c r="A796" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p12</t>
         </is>
       </c>
       <c r="B796" t="inlineStr">
@@ -50560,7 +50560,7 @@
       </c>
       <c r="E796" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="F796" t="n">
@@ -50603,7 +50603,7 @@
     <row r="797">
       <c r="A797" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p12</t>
         </is>
       </c>
       <c r="B797" t="inlineStr">
@@ -50618,31 +50618,31 @@
       </c>
       <c r="D797" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="E797" t="inlineStr">
         <is>
-          <t>chatgpt</t>
+          <t>grok</t>
         </is>
       </c>
       <c r="F797" t="n">
         <v>4</v>
       </c>
       <c r="G797" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H797" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I797" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J797" t="n">
         <v>3</v>
       </c>
       <c r="K797" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="L797" t="b">
         <v>0</v>
@@ -50666,7 +50666,7 @@
     <row r="798">
       <c r="A798" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p12</t>
         </is>
       </c>
       <c r="B798" t="inlineStr">
@@ -50686,14 +50686,14 @@
       </c>
       <c r="E798" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="F798" t="n">
         <v>4</v>
       </c>
       <c r="G798" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H798" t="n">
         <v>3</v>
@@ -50702,10 +50702,10 @@
         <v>4</v>
       </c>
       <c r="J798" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K798" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L798" t="b">
         <v>0</v>
@@ -50729,7 +50729,7 @@
     <row r="799">
       <c r="A799" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p12</t>
         </is>
       </c>
       <c r="B799" t="inlineStr">
@@ -50749,7 +50749,7 @@
       </c>
       <c r="E799" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="F799" t="n">
@@ -50759,7 +50759,7 @@
         <v>4</v>
       </c>
       <c r="H799" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I799" t="n">
         <v>4</v>
@@ -50768,7 +50768,7 @@
         <v>4</v>
       </c>
       <c r="K799" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L799" t="b">
         <v>0</v>
@@ -50792,7 +50792,7 @@
     <row r="800">
       <c r="A800" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p12</t>
         </is>
       </c>
       <c r="B800" t="inlineStr">
@@ -50807,31 +50807,31 @@
       </c>
       <c r="D800" t="inlineStr">
         <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="E800" t="inlineStr">
+        <is>
           <t>grok</t>
         </is>
       </c>
-      <c r="E800" t="inlineStr">
-        <is>
-          <t>chatgpt</t>
-        </is>
-      </c>
       <c r="F800" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G800" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H800" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I800" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J800" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K800" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="L800" t="b">
         <v>0</v>
@@ -50855,7 +50855,7 @@
     <row r="801">
       <c r="A801" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p12</t>
         </is>
       </c>
       <c r="B801" t="inlineStr">
@@ -50875,14 +50875,14 @@
       </c>
       <c r="E801" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="F801" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G801" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H801" t="n">
         <v>3</v>
@@ -50918,7 +50918,7 @@
     <row r="802">
       <c r="A802" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p12</t>
         </is>
       </c>
       <c r="B802" t="inlineStr">
@@ -50938,7 +50938,7 @@
       </c>
       <c r="E802" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="F802" t="n">
@@ -50948,7 +50948,7 @@
         <v>4</v>
       </c>
       <c r="H802" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I802" t="n">
         <v>4</v>
@@ -50957,7 +50957,7 @@
         <v>4</v>
       </c>
       <c r="K802" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L802" t="b">
         <v>0</v>
@@ -50981,7 +50981,7 @@
     <row r="803">
       <c r="A803" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p12</t>
         </is>
       </c>
       <c r="B803" t="inlineStr">
@@ -50991,17 +50991,17 @@
       </c>
       <c r="C803" t="inlineStr">
         <is>
-          <t>tune</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="D803" t="inlineStr">
         <is>
-          <t>chatgpt</t>
+          <t>grok</t>
         </is>
       </c>
       <c r="E803" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="F803" t="n">
@@ -51044,7 +51044,7 @@
     <row r="804">
       <c r="A804" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p12</t>
         </is>
       </c>
       <c r="B804" t="inlineStr">
@@ -51064,7 +51064,7 @@
       </c>
       <c r="E804" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="F804" t="n">
@@ -51107,7 +51107,7 @@
     <row r="805">
       <c r="A805" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p12</t>
         </is>
       </c>
       <c r="B805" t="inlineStr">
@@ -51127,7 +51127,7 @@
       </c>
       <c r="E805" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="F805" t="n">
@@ -51170,7 +51170,7 @@
     <row r="806">
       <c r="A806" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p12</t>
         </is>
       </c>
       <c r="B806" t="inlineStr">
@@ -51185,12 +51185,12 @@
       </c>
       <c r="D806" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="E806" t="inlineStr">
         <is>
-          <t>chatgpt</t>
+          <t>grok</t>
         </is>
       </c>
       <c r="F806" t="n">
@@ -51203,13 +51203,13 @@
         <v>4</v>
       </c>
       <c r="I806" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J806" t="n">
         <v>4</v>
       </c>
       <c r="K806" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L806" t="b">
         <v>0</v>
@@ -51233,7 +51233,7 @@
     <row r="807">
       <c r="A807" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p12</t>
         </is>
       </c>
       <c r="B807" t="inlineStr">
@@ -51253,14 +51253,14 @@
       </c>
       <c r="E807" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="F807" t="n">
         <v>4</v>
       </c>
       <c r="G807" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H807" t="n">
         <v>4</v>
@@ -51269,10 +51269,10 @@
         <v>4</v>
       </c>
       <c r="J807" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K807" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L807" t="b">
         <v>0</v>
@@ -51296,7 +51296,7 @@
     <row r="808">
       <c r="A808" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p12</t>
         </is>
       </c>
       <c r="B808" t="inlineStr">
@@ -51316,7 +51316,7 @@
       </c>
       <c r="E808" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="F808" t="n">
@@ -51359,7 +51359,7 @@
     <row r="809">
       <c r="A809" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p12</t>
         </is>
       </c>
       <c r="B809" t="inlineStr">
@@ -51374,31 +51374,31 @@
       </c>
       <c r="D809" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="E809" t="inlineStr">
         <is>
-          <t>chatgpt</t>
+          <t>grok</t>
         </is>
       </c>
       <c r="F809" t="n">
         <v>4</v>
       </c>
       <c r="G809" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H809" t="n">
         <v>4</v>
       </c>
       <c r="I809" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J809" t="n">
         <v>4</v>
       </c>
       <c r="K809" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L809" t="b">
         <v>0</v>
@@ -51422,7 +51422,7 @@
     <row r="810">
       <c r="A810" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p12</t>
         </is>
       </c>
       <c r="B810" t="inlineStr">
@@ -51442,14 +51442,14 @@
       </c>
       <c r="E810" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="F810" t="n">
         <v>4</v>
       </c>
       <c r="G810" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H810" t="n">
         <v>4</v>
@@ -51458,10 +51458,10 @@
         <v>4</v>
       </c>
       <c r="J810" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K810" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L810" t="b">
         <v>0</v>
@@ -51485,7 +51485,7 @@
     <row r="811">
       <c r="A811" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p12</t>
         </is>
       </c>
       <c r="B811" t="inlineStr">
@@ -51505,7 +51505,7 @@
       </c>
       <c r="E811" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="F811" t="n">
@@ -51548,7 +51548,7 @@
     <row r="812">
       <c r="A812" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p12</t>
         </is>
       </c>
       <c r="B812" t="inlineStr">
@@ -51563,14 +51563,14 @@
       </c>
       <c r="D812" t="inlineStr">
         <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="E812" t="inlineStr">
+        <is>
           <t>grok</t>
         </is>
       </c>
-      <c r="E812" t="inlineStr">
-        <is>
-          <t>chatgpt</t>
-        </is>
-      </c>
       <c r="F812" t="n">
         <v>4</v>
       </c>
@@ -51578,16 +51578,16 @@
         <v>4</v>
       </c>
       <c r="H812" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I812" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J812" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K812" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L812" t="b">
         <v>0</v>
@@ -51611,7 +51611,7 @@
     <row r="813">
       <c r="A813" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p12</t>
         </is>
       </c>
       <c r="B813" t="inlineStr">
@@ -51631,14 +51631,14 @@
       </c>
       <c r="E813" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="F813" t="n">
         <v>4</v>
       </c>
       <c r="G813" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H813" t="n">
         <v>4</v>
@@ -51647,10 +51647,10 @@
         <v>4</v>
       </c>
       <c r="J813" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K813" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L813" t="b">
         <v>0</v>
@@ -51674,7 +51674,7 @@
     <row r="814">
       <c r="A814" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p12</t>
         </is>
       </c>
       <c r="B814" t="inlineStr">
@@ -51694,7 +51694,7 @@
       </c>
       <c r="E814" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="F814" t="n">
@@ -51737,27 +51737,27 @@
     <row r="815">
       <c r="A815" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p12</t>
         </is>
       </c>
       <c r="B815" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="C815" t="inlineStr">
         <is>
-          <t>generate</t>
+          <t>tune</t>
         </is>
       </c>
       <c r="D815" t="inlineStr">
         <is>
-          <t>chatgpt</t>
+          <t>grok</t>
         </is>
       </c>
       <c r="E815" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="F815" t="n">
@@ -51800,7 +51800,7 @@
     <row r="816">
       <c r="A816" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p12</t>
         </is>
       </c>
       <c r="B816" t="inlineStr">
@@ -51820,7 +51820,7 @@
       </c>
       <c r="E816" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="F816" t="n">
@@ -51863,7 +51863,7 @@
     <row r="817">
       <c r="A817" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p12</t>
         </is>
       </c>
       <c r="B817" t="inlineStr">
@@ -51883,7 +51883,7 @@
       </c>
       <c r="E817" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="F817" t="n">
@@ -51926,7 +51926,7 @@
     <row r="818">
       <c r="A818" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p12</t>
         </is>
       </c>
       <c r="B818" t="inlineStr">
@@ -51941,31 +51941,31 @@
       </c>
       <c r="D818" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="E818" t="inlineStr">
         <is>
-          <t>chatgpt</t>
+          <t>grok</t>
         </is>
       </c>
       <c r="F818" t="n">
         <v>4</v>
       </c>
       <c r="G818" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H818" t="n">
         <v>4</v>
       </c>
       <c r="I818" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J818" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K818" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L818" t="b">
         <v>0</v>
@@ -51989,7 +51989,7 @@
     <row r="819">
       <c r="A819" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p12</t>
         </is>
       </c>
       <c r="B819" t="inlineStr">
@@ -52009,26 +52009,26 @@
       </c>
       <c r="E819" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="F819" t="n">
         <v>4</v>
       </c>
       <c r="G819" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H819" t="n">
         <v>4</v>
       </c>
       <c r="I819" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J819" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K819" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="L819" t="b">
         <v>0</v>
@@ -52052,7 +52052,7 @@
     <row r="820">
       <c r="A820" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p12</t>
         </is>
       </c>
       <c r="B820" t="inlineStr">
@@ -52072,7 +52072,7 @@
       </c>
       <c r="E820" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="F820" t="n">
@@ -52088,10 +52088,10 @@
         <v>4</v>
       </c>
       <c r="J820" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K820" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L820" t="b">
         <v>0</v>
@@ -52115,7 +52115,7 @@
     <row r="821">
       <c r="A821" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p12</t>
         </is>
       </c>
       <c r="B821" t="inlineStr">
@@ -52130,12 +52130,12 @@
       </c>
       <c r="D821" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="E821" t="inlineStr">
         <is>
-          <t>chatgpt</t>
+          <t>grok</t>
         </is>
       </c>
       <c r="F821" t="n">
@@ -52151,10 +52151,10 @@
         <v>4</v>
       </c>
       <c r="J821" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K821" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L821" t="b">
         <v>0</v>
@@ -52178,7 +52178,7 @@
     <row r="822">
       <c r="A822" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p12</t>
         </is>
       </c>
       <c r="B822" t="inlineStr">
@@ -52198,26 +52198,26 @@
       </c>
       <c r="E822" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="F822" t="n">
         <v>4</v>
       </c>
       <c r="G822" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H822" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I822" t="n">
         <v>4</v>
       </c>
       <c r="J822" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K822" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="L822" t="b">
         <v>0</v>
@@ -52241,7 +52241,7 @@
     <row r="823">
       <c r="A823" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p12</t>
         </is>
       </c>
       <c r="B823" t="inlineStr">
@@ -52261,7 +52261,7 @@
       </c>
       <c r="E823" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="F823" t="n">
@@ -52277,10 +52277,10 @@
         <v>4</v>
       </c>
       <c r="J823" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K823" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L823" t="b">
         <v>0</v>
@@ -52304,7 +52304,7 @@
     <row r="824">
       <c r="A824" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p12</t>
         </is>
       </c>
       <c r="B824" t="inlineStr">
@@ -52319,31 +52319,31 @@
       </c>
       <c r="D824" t="inlineStr">
         <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="E824" t="inlineStr">
+        <is>
           <t>grok</t>
         </is>
       </c>
-      <c r="E824" t="inlineStr">
-        <is>
-          <t>chatgpt</t>
-        </is>
-      </c>
       <c r="F824" t="n">
         <v>4</v>
       </c>
       <c r="G824" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H824" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I824" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J824" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K824" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L824" t="b">
         <v>0</v>
@@ -52367,7 +52367,7 @@
     <row r="825">
       <c r="A825" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p12</t>
         </is>
       </c>
       <c r="B825" t="inlineStr">
@@ -52387,14 +52387,14 @@
       </c>
       <c r="E825" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="F825" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G825" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H825" t="n">
         <v>3</v>
@@ -52430,7 +52430,7 @@
     <row r="826">
       <c r="A826" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p12</t>
         </is>
       </c>
       <c r="B826" t="inlineStr">
@@ -52450,7 +52450,7 @@
       </c>
       <c r="E826" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="F826" t="n">
@@ -52460,16 +52460,16 @@
         <v>4</v>
       </c>
       <c r="H826" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I826" t="n">
         <v>4</v>
       </c>
       <c r="J826" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K826" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L826" t="b">
         <v>0</v>
@@ -52493,7 +52493,7 @@
     <row r="827">
       <c r="A827" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p12</t>
         </is>
       </c>
       <c r="B827" t="inlineStr">
@@ -52503,17 +52503,17 @@
       </c>
       <c r="C827" t="inlineStr">
         <is>
-          <t>tune</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="D827" t="inlineStr">
         <is>
-          <t>chatgpt</t>
+          <t>grok</t>
         </is>
       </c>
       <c r="E827" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="F827" t="n">
@@ -52556,7 +52556,7 @@
     <row r="828">
       <c r="A828" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p12</t>
         </is>
       </c>
       <c r="B828" t="inlineStr">
@@ -52576,7 +52576,7 @@
       </c>
       <c r="E828" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="F828" t="n">
@@ -52619,7 +52619,7 @@
     <row r="829">
       <c r="A829" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p12</t>
         </is>
       </c>
       <c r="B829" t="inlineStr">
@@ -52639,7 +52639,7 @@
       </c>
       <c r="E829" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="F829" t="n">
@@ -52682,7 +52682,7 @@
     <row r="830">
       <c r="A830" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p12</t>
         </is>
       </c>
       <c r="B830" t="inlineStr">
@@ -52697,12 +52697,12 @@
       </c>
       <c r="D830" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="E830" t="inlineStr">
         <is>
-          <t>chatgpt</t>
+          <t>grok</t>
         </is>
       </c>
       <c r="F830" t="n">
@@ -52712,16 +52712,16 @@
         <v>4</v>
       </c>
       <c r="H830" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I830" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J830" t="n">
         <v>4</v>
       </c>
       <c r="K830" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L830" t="b">
         <v>0</v>
@@ -52745,7 +52745,7 @@
     <row r="831">
       <c r="A831" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p12</t>
         </is>
       </c>
       <c r="B831" t="inlineStr">
@@ -52765,14 +52765,14 @@
       </c>
       <c r="E831" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="F831" t="n">
         <v>4</v>
       </c>
       <c r="G831" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H831" t="n">
         <v>4</v>
@@ -52781,10 +52781,10 @@
         <v>4</v>
       </c>
       <c r="J831" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K831" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L831" t="b">
         <v>0</v>
@@ -52808,7 +52808,7 @@
     <row r="832">
       <c r="A832" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p12</t>
         </is>
       </c>
       <c r="B832" t="inlineStr">
@@ -52828,7 +52828,7 @@
       </c>
       <c r="E832" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="F832" t="n">
@@ -52871,7 +52871,7 @@
     <row r="833">
       <c r="A833" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p12</t>
         </is>
       </c>
       <c r="B833" t="inlineStr">
@@ -52886,12 +52886,12 @@
       </c>
       <c r="D833" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="E833" t="inlineStr">
         <is>
-          <t>chatgpt</t>
+          <t>grok</t>
         </is>
       </c>
       <c r="F833" t="n">
@@ -52901,7 +52901,7 @@
         <v>4</v>
       </c>
       <c r="H833" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I833" t="n">
         <v>4</v>
@@ -52910,7 +52910,7 @@
         <v>4</v>
       </c>
       <c r="K833" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L833" t="b">
         <v>0</v>
@@ -52934,7 +52934,7 @@
     <row r="834">
       <c r="A834" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p12</t>
         </is>
       </c>
       <c r="B834" t="inlineStr">
@@ -52954,14 +52954,14 @@
       </c>
       <c r="E834" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="F834" t="n">
         <v>4</v>
       </c>
       <c r="G834" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H834" t="n">
         <v>4</v>
@@ -52970,10 +52970,10 @@
         <v>4</v>
       </c>
       <c r="J834" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K834" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L834" t="b">
         <v>0</v>
@@ -52997,7 +52997,7 @@
     <row r="835">
       <c r="A835" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p12</t>
         </is>
       </c>
       <c r="B835" t="inlineStr">
@@ -53017,14 +53017,14 @@
       </c>
       <c r="E835" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="F835" t="n">
         <v>4</v>
       </c>
       <c r="G835" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H835" t="n">
         <v>4</v>
@@ -53033,10 +53033,10 @@
         <v>4</v>
       </c>
       <c r="J835" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K835" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L835" t="b">
         <v>0</v>
@@ -53060,7 +53060,7 @@
     <row r="836">
       <c r="A836" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p12</t>
         </is>
       </c>
       <c r="B836" t="inlineStr">
@@ -53075,14 +53075,14 @@
       </c>
       <c r="D836" t="inlineStr">
         <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="E836" t="inlineStr">
+        <is>
           <t>grok</t>
         </is>
       </c>
-      <c r="E836" t="inlineStr">
-        <is>
-          <t>chatgpt</t>
-        </is>
-      </c>
       <c r="F836" t="n">
         <v>4</v>
       </c>
@@ -53090,7 +53090,7 @@
         <v>4</v>
       </c>
       <c r="H836" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I836" t="n">
         <v>4</v>
@@ -53099,7 +53099,7 @@
         <v>4</v>
       </c>
       <c r="K836" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L836" t="b">
         <v>0</v>
@@ -53123,7 +53123,7 @@
     <row r="837">
       <c r="A837" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p12</t>
         </is>
       </c>
       <c r="B837" t="inlineStr">
@@ -53143,7 +53143,7 @@
       </c>
       <c r="E837" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="F837" t="n">
@@ -53186,7 +53186,7 @@
     <row r="838">
       <c r="A838" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p12</t>
         </is>
       </c>
       <c r="B838" t="inlineStr">
@@ -53206,7 +53206,7 @@
       </c>
       <c r="E838" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="F838" t="n">
@@ -53249,27 +53249,27 @@
     <row r="839">
       <c r="A839" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p12</t>
         </is>
       </c>
       <c r="B839" t="inlineStr">
         <is>
-          <t>A3</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="C839" t="inlineStr">
         <is>
-          <t>generate</t>
+          <t>tune</t>
         </is>
       </c>
       <c r="D839" t="inlineStr">
         <is>
-          <t>chatgpt</t>
+          <t>grok</t>
         </is>
       </c>
       <c r="E839" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="F839" t="n">
@@ -53279,7 +53279,7 @@
         <v>4</v>
       </c>
       <c r="H839" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I839" t="n">
         <v>4</v>
@@ -53288,7 +53288,7 @@
         <v>4</v>
       </c>
       <c r="K839" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L839" t="b">
         <v>0</v>
@@ -53312,7 +53312,7 @@
     <row r="840">
       <c r="A840" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p12</t>
         </is>
       </c>
       <c r="B840" t="inlineStr">
@@ -53332,7 +53332,7 @@
       </c>
       <c r="E840" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="F840" t="n">
@@ -53342,7 +53342,7 @@
         <v>4</v>
       </c>
       <c r="H840" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I840" t="n">
         <v>4</v>
@@ -53351,7 +53351,7 @@
         <v>4</v>
       </c>
       <c r="K840" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L840" t="b">
         <v>0</v>
@@ -53375,7 +53375,7 @@
     <row r="841">
       <c r="A841" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p12</t>
         </is>
       </c>
       <c r="B841" t="inlineStr">
@@ -53395,7 +53395,7 @@
       </c>
       <c r="E841" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="F841" t="n">
@@ -53438,7 +53438,7 @@
     <row r="842">
       <c r="A842" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p12</t>
         </is>
       </c>
       <c r="B842" t="inlineStr">
@@ -53453,31 +53453,31 @@
       </c>
       <c r="D842" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="E842" t="inlineStr">
         <is>
-          <t>chatgpt</t>
+          <t>grok</t>
         </is>
       </c>
       <c r="F842" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G842" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H842" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I842" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J842" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K842" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="L842" t="b">
         <v>0</v>
@@ -53501,7 +53501,7 @@
     <row r="843">
       <c r="A843" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p12</t>
         </is>
       </c>
       <c r="B843" t="inlineStr">
@@ -53521,26 +53521,26 @@
       </c>
       <c r="E843" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="F843" t="n">
         <v>4</v>
       </c>
       <c r="G843" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H843" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I843" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J843" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K843" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="L843" t="b">
         <v>0</v>
@@ -53564,7 +53564,7 @@
     <row r="844">
       <c r="A844" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p12</t>
         </is>
       </c>
       <c r="B844" t="inlineStr">
@@ -53584,26 +53584,26 @@
       </c>
       <c r="E844" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="F844" t="n">
         <v>4</v>
       </c>
       <c r="G844" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H844" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I844" t="n">
         <v>4</v>
       </c>
       <c r="J844" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K844" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="L844" t="b">
         <v>0</v>
@@ -53627,7 +53627,7 @@
     <row r="845">
       <c r="A845" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p12</t>
         </is>
       </c>
       <c r="B845" t="inlineStr">
@@ -53642,31 +53642,31 @@
       </c>
       <c r="D845" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="E845" t="inlineStr">
         <is>
-          <t>chatgpt</t>
+          <t>grok</t>
         </is>
       </c>
       <c r="F845" t="n">
         <v>4</v>
       </c>
       <c r="G845" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H845" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I845" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J845" t="n">
         <v>3</v>
       </c>
       <c r="K845" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="L845" t="b">
         <v>0</v>
@@ -53690,7 +53690,7 @@
     <row r="846">
       <c r="A846" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p12</t>
         </is>
       </c>
       <c r="B846" t="inlineStr">
@@ -53710,17 +53710,17 @@
       </c>
       <c r="E846" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="F846" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G846" t="n">
         <v>3</v>
       </c>
       <c r="H846" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I846" t="n">
         <v>3</v>
@@ -53729,7 +53729,7 @@
         <v>3</v>
       </c>
       <c r="K846" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L846" t="b">
         <v>0</v>
@@ -53753,7 +53753,7 @@
     <row r="847">
       <c r="A847" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p12</t>
         </is>
       </c>
       <c r="B847" t="inlineStr">
@@ -53773,26 +53773,26 @@
       </c>
       <c r="E847" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="F847" t="n">
         <v>4</v>
       </c>
       <c r="G847" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H847" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I847" t="n">
         <v>4</v>
       </c>
       <c r="J847" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K847" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="L847" t="b">
         <v>0</v>
@@ -53816,7 +53816,7 @@
     <row r="848">
       <c r="A848" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p12</t>
         </is>
       </c>
       <c r="B848" t="inlineStr">
@@ -53831,31 +53831,31 @@
       </c>
       <c r="D848" t="inlineStr">
         <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="E848" t="inlineStr">
+        <is>
           <t>grok</t>
         </is>
       </c>
-      <c r="E848" t="inlineStr">
-        <is>
-          <t>chatgpt</t>
-        </is>
-      </c>
       <c r="F848" t="n">
         <v>4</v>
       </c>
       <c r="G848" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H848" t="n">
         <v>3</v>
       </c>
       <c r="I848" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J848" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K848" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="L848" t="b">
         <v>0</v>
@@ -53879,7 +53879,7 @@
     <row r="849">
       <c r="A849" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p12</t>
         </is>
       </c>
       <c r="B849" t="inlineStr">
@@ -53899,17 +53899,17 @@
       </c>
       <c r="E849" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="F849" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G849" t="n">
         <v>3</v>
       </c>
       <c r="H849" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I849" t="n">
         <v>3</v>
@@ -53918,7 +53918,7 @@
         <v>3</v>
       </c>
       <c r="K849" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L849" t="b">
         <v>0</v>
@@ -53942,7 +53942,7 @@
     <row r="850">
       <c r="A850" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p12</t>
         </is>
       </c>
       <c r="B850" t="inlineStr">
@@ -53962,7 +53962,7 @@
       </c>
       <c r="E850" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="F850" t="n">
@@ -53972,16 +53972,16 @@
         <v>4</v>
       </c>
       <c r="H850" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I850" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J850" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K850" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="L850" t="b">
         <v>0</v>
@@ -54005,7 +54005,7 @@
     <row r="851">
       <c r="A851" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p12</t>
         </is>
       </c>
       <c r="B851" t="inlineStr">
@@ -54015,17 +54015,17 @@
       </c>
       <c r="C851" t="inlineStr">
         <is>
-          <t>tune</t>
+          <t>generate</t>
         </is>
       </c>
       <c r="D851" t="inlineStr">
         <is>
-          <t>chatgpt</t>
+          <t>grok</t>
         </is>
       </c>
       <c r="E851" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="F851" t="n">
@@ -54038,13 +54038,13 @@
         <v>4</v>
       </c>
       <c r="I851" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="J851" t="n">
         <v>4</v>
       </c>
       <c r="K851" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="L851" t="b">
         <v>0</v>
@@ -54068,7 +54068,7 @@
     <row r="852">
       <c r="A852" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p12</t>
         </is>
       </c>
       <c r="B852" t="inlineStr">
@@ -54088,7 +54088,7 @@
       </c>
       <c r="E852" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="F852" t="n">
@@ -54131,7 +54131,7 @@
     <row r="853">
       <c r="A853" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p12</t>
         </is>
       </c>
       <c r="B853" t="inlineStr">
@@ -54151,7 +54151,7 @@
       </c>
       <c r="E853" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="F853" t="n">
@@ -54194,7 +54194,7 @@
     <row r="854">
       <c r="A854" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p12</t>
         </is>
       </c>
       <c r="B854" t="inlineStr">
@@ -54209,12 +54209,12 @@
       </c>
       <c r="D854" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="E854" t="inlineStr">
         <is>
-          <t>chatgpt</t>
+          <t>grok</t>
         </is>
       </c>
       <c r="F854" t="n">
@@ -54224,16 +54224,16 @@
         <v>4</v>
       </c>
       <c r="H854" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I854" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J854" t="n">
         <v>4</v>
       </c>
       <c r="K854" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L854" t="b">
         <v>0</v>
@@ -54257,7 +54257,7 @@
     <row r="855">
       <c r="A855" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p12</t>
         </is>
       </c>
       <c r="B855" t="inlineStr">
@@ -54277,7 +54277,7 @@
       </c>
       <c r="E855" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="F855" t="n">
@@ -54320,7 +54320,7 @@
     <row r="856">
       <c r="A856" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p12</t>
         </is>
       </c>
       <c r="B856" t="inlineStr">
@@ -54340,7 +54340,7 @@
       </c>
       <c r="E856" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="F856" t="n">
@@ -54383,7 +54383,7 @@
     <row r="857">
       <c r="A857" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p12</t>
         </is>
       </c>
       <c r="B857" t="inlineStr">
@@ -54398,12 +54398,12 @@
       </c>
       <c r="D857" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="E857" t="inlineStr">
         <is>
-          <t>chatgpt</t>
+          <t>grok</t>
         </is>
       </c>
       <c r="F857" t="n">
@@ -54446,7 +54446,7 @@
     <row r="858">
       <c r="A858" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p12</t>
         </is>
       </c>
       <c r="B858" t="inlineStr">
@@ -54466,26 +54466,26 @@
       </c>
       <c r="E858" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="F858" t="n">
         <v>4</v>
       </c>
       <c r="G858" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H858" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I858" t="n">
         <v>4</v>
       </c>
       <c r="J858" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K858" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="L858" t="b">
         <v>0</v>
@@ -54509,7 +54509,7 @@
     <row r="859">
       <c r="A859" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p12</t>
         </is>
       </c>
       <c r="B859" t="inlineStr">
@@ -54529,7 +54529,7 @@
       </c>
       <c r="E859" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="F859" t="n">
@@ -54542,13 +54542,13 @@
         <v>4</v>
       </c>
       <c r="I859" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J859" t="n">
         <v>4</v>
       </c>
       <c r="K859" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L859" t="b">
         <v>0</v>
@@ -54572,7 +54572,7 @@
     <row r="860">
       <c r="A860" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p12</t>
         </is>
       </c>
       <c r="B860" t="inlineStr">
@@ -54587,14 +54587,14 @@
       </c>
       <c r="D860" t="inlineStr">
         <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="E860" t="inlineStr">
+        <is>
           <t>grok</t>
         </is>
       </c>
-      <c r="E860" t="inlineStr">
-        <is>
-          <t>chatgpt</t>
-        </is>
-      </c>
       <c r="F860" t="n">
         <v>4</v>
       </c>
@@ -54608,10 +54608,10 @@
         <v>4</v>
       </c>
       <c r="J860" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K860" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L860" t="b">
         <v>0</v>
@@ -54635,7 +54635,7 @@
     <row r="861">
       <c r="A861" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p12</t>
         </is>
       </c>
       <c r="B861" t="inlineStr">
@@ -54655,7 +54655,7 @@
       </c>
       <c r="E861" t="inlineStr">
         <is>
-          <t>claude</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="F861" t="n">
@@ -54668,13 +54668,13 @@
         <v>4</v>
       </c>
       <c r="I861" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J861" t="n">
         <v>4</v>
       </c>
       <c r="K861" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L861" t="b">
         <v>0</v>
@@ -54698,7 +54698,7 @@
     <row r="862">
       <c r="A862" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p12</t>
         </is>
       </c>
       <c r="B862" t="inlineStr">
@@ -54718,7 +54718,7 @@
       </c>
       <c r="E862" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="F862" t="n">
@@ -54755,6 +54755,69 @@
         <v>0</v>
       </c>
       <c r="Q862" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" t="inlineStr">
+        <is>
+          <t>p12</t>
+        </is>
+      </c>
+      <c r="B863" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C863" t="inlineStr">
+        <is>
+          <t>tune</t>
+        </is>
+      </c>
+      <c r="D863" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="E863" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="F863" t="n">
+        <v>4</v>
+      </c>
+      <c r="G863" t="n">
+        <v>4</v>
+      </c>
+      <c r="H863" t="n">
+        <v>4</v>
+      </c>
+      <c r="I863" t="n">
+        <v>4</v>
+      </c>
+      <c r="J863" t="n">
+        <v>4</v>
+      </c>
+      <c r="K863" t="n">
+        <v>20</v>
+      </c>
+      <c r="L863" t="b">
+        <v>0</v>
+      </c>
+      <c r="M863" t="b">
+        <v>0</v>
+      </c>
+      <c r="N863" t="b">
+        <v>0</v>
+      </c>
+      <c r="O863" t="b">
+        <v>0</v>
+      </c>
+      <c r="P863" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q863" t="b">
         <v>0</v>
       </c>
     </row>

--- a/src/scores_all.xlsx
+++ b/src/scores_all.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q863"/>
+  <dimension ref="A1:Q935"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50288,7 +50288,7 @@
     <row r="792">
       <c r="A792" t="inlineStr">
         <is>
-          <t>p12</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="B792" t="inlineStr">
@@ -50351,7 +50351,7 @@
     <row r="793">
       <c r="A793" t="inlineStr">
         <is>
-          <t>p12</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="B793" t="inlineStr">
@@ -50414,7 +50414,7 @@
     <row r="794">
       <c r="A794" t="inlineStr">
         <is>
-          <t>p12</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="B794" t="inlineStr">
@@ -50477,7 +50477,7 @@
     <row r="795">
       <c r="A795" t="inlineStr">
         <is>
-          <t>p12</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="B795" t="inlineStr">
@@ -50513,10 +50513,10 @@
         <v>3</v>
       </c>
       <c r="J795" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K795" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L795" t="b">
         <v>0</v>
@@ -50540,7 +50540,7 @@
     <row r="796">
       <c r="A796" t="inlineStr">
         <is>
-          <t>p12</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="B796" t="inlineStr">
@@ -50603,7 +50603,7 @@
     <row r="797">
       <c r="A797" t="inlineStr">
         <is>
-          <t>p12</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="B797" t="inlineStr">
@@ -50639,10 +50639,10 @@
         <v>4</v>
       </c>
       <c r="J797" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K797" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L797" t="b">
         <v>0</v>
@@ -50666,7 +50666,7 @@
     <row r="798">
       <c r="A798" t="inlineStr">
         <is>
-          <t>p12</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="B798" t="inlineStr">
@@ -50690,22 +50690,22 @@
         </is>
       </c>
       <c r="F798" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G798" t="n">
         <v>3</v>
       </c>
       <c r="H798" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I798" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J798" t="n">
         <v>3</v>
       </c>
       <c r="K798" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="L798" t="b">
         <v>0</v>
@@ -50729,7 +50729,7 @@
     <row r="799">
       <c r="A799" t="inlineStr">
         <is>
-          <t>p12</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="B799" t="inlineStr">
@@ -50792,7 +50792,7 @@
     <row r="800">
       <c r="A800" t="inlineStr">
         <is>
-          <t>p12</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="B800" t="inlineStr">
@@ -50855,7 +50855,7 @@
     <row r="801">
       <c r="A801" t="inlineStr">
         <is>
-          <t>p12</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="B801" t="inlineStr">
@@ -50888,13 +50888,13 @@
         <v>3</v>
       </c>
       <c r="I801" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J801" t="n">
         <v>3</v>
       </c>
       <c r="K801" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L801" t="b">
         <v>0</v>
@@ -50918,7 +50918,7 @@
     <row r="802">
       <c r="A802" t="inlineStr">
         <is>
-          <t>p12</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="B802" t="inlineStr">
@@ -50981,7 +50981,7 @@
     <row r="803">
       <c r="A803" t="inlineStr">
         <is>
-          <t>p12</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="B803" t="inlineStr">
@@ -51044,7 +51044,7 @@
     <row r="804">
       <c r="A804" t="inlineStr">
         <is>
-          <t>p12</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="B804" t="inlineStr">
@@ -51107,7 +51107,7 @@
     <row r="805">
       <c r="A805" t="inlineStr">
         <is>
-          <t>p12</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="B805" t="inlineStr">
@@ -51170,7 +51170,7 @@
     <row r="806">
       <c r="A806" t="inlineStr">
         <is>
-          <t>p12</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="B806" t="inlineStr">
@@ -51233,7 +51233,7 @@
     <row r="807">
       <c r="A807" t="inlineStr">
         <is>
-          <t>p12</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="B807" t="inlineStr">
@@ -51263,7 +51263,7 @@
         <v>3</v>
       </c>
       <c r="H807" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I807" t="n">
         <v>4</v>
@@ -51272,7 +51272,7 @@
         <v>3</v>
       </c>
       <c r="K807" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L807" t="b">
         <v>0</v>
@@ -51296,7 +51296,7 @@
     <row r="808">
       <c r="A808" t="inlineStr">
         <is>
-          <t>p12</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="B808" t="inlineStr">
@@ -51359,7 +51359,7 @@
     <row r="809">
       <c r="A809" t="inlineStr">
         <is>
-          <t>p12</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="B809" t="inlineStr">
@@ -51422,7 +51422,7 @@
     <row r="810">
       <c r="A810" t="inlineStr">
         <is>
-          <t>p12</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="B810" t="inlineStr">
@@ -51455,13 +51455,13 @@
         <v>4</v>
       </c>
       <c r="I810" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J810" t="n">
         <v>3</v>
       </c>
       <c r="K810" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L810" t="b">
         <v>0</v>
@@ -51485,7 +51485,7 @@
     <row r="811">
       <c r="A811" t="inlineStr">
         <is>
-          <t>p12</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="B811" t="inlineStr">
@@ -51512,19 +51512,19 @@
         <v>4</v>
       </c>
       <c r="G811" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H811" t="n">
         <v>4</v>
       </c>
       <c r="I811" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J811" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K811" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="L811" t="b">
         <v>0</v>
@@ -51548,7 +51548,7 @@
     <row r="812">
       <c r="A812" t="inlineStr">
         <is>
-          <t>p12</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="B812" t="inlineStr">
@@ -51611,7 +51611,7 @@
     <row r="813">
       <c r="A813" t="inlineStr">
         <is>
-          <t>p12</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="B813" t="inlineStr">
@@ -51638,7 +51638,7 @@
         <v>4</v>
       </c>
       <c r="G813" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H813" t="n">
         <v>4</v>
@@ -51647,10 +51647,10 @@
         <v>4</v>
       </c>
       <c r="J813" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K813" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L813" t="b">
         <v>0</v>
@@ -51674,7 +51674,7 @@
     <row r="814">
       <c r="A814" t="inlineStr">
         <is>
-          <t>p12</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="B814" t="inlineStr">
@@ -51737,7 +51737,7 @@
     <row r="815">
       <c r="A815" t="inlineStr">
         <is>
-          <t>p12</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="B815" t="inlineStr">
@@ -51800,7 +51800,7 @@
     <row r="816">
       <c r="A816" t="inlineStr">
         <is>
-          <t>p12</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="B816" t="inlineStr">
@@ -51863,7 +51863,7 @@
     <row r="817">
       <c r="A817" t="inlineStr">
         <is>
-          <t>p12</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="B817" t="inlineStr">
@@ -51926,7 +51926,7 @@
     <row r="818">
       <c r="A818" t="inlineStr">
         <is>
-          <t>p12</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="B818" t="inlineStr">
@@ -51989,7 +51989,7 @@
     <row r="819">
       <c r="A819" t="inlineStr">
         <is>
-          <t>p12</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="B819" t="inlineStr">
@@ -52052,7 +52052,7 @@
     <row r="820">
       <c r="A820" t="inlineStr">
         <is>
-          <t>p12</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="B820" t="inlineStr">
@@ -52088,10 +52088,10 @@
         <v>4</v>
       </c>
       <c r="J820" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K820" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L820" t="b">
         <v>0</v>
@@ -52115,7 +52115,7 @@
     <row r="821">
       <c r="A821" t="inlineStr">
         <is>
-          <t>p12</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="B821" t="inlineStr">
@@ -52178,7 +52178,7 @@
     <row r="822">
       <c r="A822" t="inlineStr">
         <is>
-          <t>p12</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="B822" t="inlineStr">
@@ -52211,13 +52211,13 @@
         <v>3</v>
       </c>
       <c r="I822" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J822" t="n">
         <v>3</v>
       </c>
       <c r="K822" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L822" t="b">
         <v>0</v>
@@ -52241,7 +52241,7 @@
     <row r="823">
       <c r="A823" t="inlineStr">
         <is>
-          <t>p12</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="B823" t="inlineStr">
@@ -52277,10 +52277,10 @@
         <v>4</v>
       </c>
       <c r="J823" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K823" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L823" t="b">
         <v>0</v>
@@ -52304,7 +52304,7 @@
     <row r="824">
       <c r="A824" t="inlineStr">
         <is>
-          <t>p12</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="B824" t="inlineStr">
@@ -52367,7 +52367,7 @@
     <row r="825">
       <c r="A825" t="inlineStr">
         <is>
-          <t>p12</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="B825" t="inlineStr">
@@ -52394,7 +52394,7 @@
         <v>4</v>
       </c>
       <c r="G825" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H825" t="n">
         <v>3</v>
@@ -52403,10 +52403,10 @@
         <v>3</v>
       </c>
       <c r="J825" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K825" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L825" t="b">
         <v>0</v>
@@ -52430,7 +52430,7 @@
     <row r="826">
       <c r="A826" t="inlineStr">
         <is>
-          <t>p12</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="B826" t="inlineStr">
@@ -52460,16 +52460,16 @@
         <v>4</v>
       </c>
       <c r="H826" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I826" t="n">
         <v>4</v>
       </c>
       <c r="J826" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K826" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L826" t="b">
         <v>0</v>
@@ -52493,7 +52493,7 @@
     <row r="827">
       <c r="A827" t="inlineStr">
         <is>
-          <t>p12</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="B827" t="inlineStr">
@@ -52556,7 +52556,7 @@
     <row r="828">
       <c r="A828" t="inlineStr">
         <is>
-          <t>p12</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="B828" t="inlineStr">
@@ -52619,7 +52619,7 @@
     <row r="829">
       <c r="A829" t="inlineStr">
         <is>
-          <t>p12</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="B829" t="inlineStr">
@@ -52682,7 +52682,7 @@
     <row r="830">
       <c r="A830" t="inlineStr">
         <is>
-          <t>p12</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="B830" t="inlineStr">
@@ -52745,7 +52745,7 @@
     <row r="831">
       <c r="A831" t="inlineStr">
         <is>
-          <t>p12</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="B831" t="inlineStr">
@@ -52772,7 +52772,7 @@
         <v>4</v>
       </c>
       <c r="G831" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H831" t="n">
         <v>4</v>
@@ -52781,10 +52781,10 @@
         <v>4</v>
       </c>
       <c r="J831" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K831" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L831" t="b">
         <v>0</v>
@@ -52808,7 +52808,7 @@
     <row r="832">
       <c r="A832" t="inlineStr">
         <is>
-          <t>p12</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="B832" t="inlineStr">
@@ -52871,7 +52871,7 @@
     <row r="833">
       <c r="A833" t="inlineStr">
         <is>
-          <t>p12</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="B833" t="inlineStr">
@@ -52934,7 +52934,7 @@
     <row r="834">
       <c r="A834" t="inlineStr">
         <is>
-          <t>p12</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="B834" t="inlineStr">
@@ -52970,10 +52970,10 @@
         <v>4</v>
       </c>
       <c r="J834" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K834" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L834" t="b">
         <v>0</v>
@@ -52997,7 +52997,7 @@
     <row r="835">
       <c r="A835" t="inlineStr">
         <is>
-          <t>p12</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="B835" t="inlineStr">
@@ -53024,7 +53024,7 @@
         <v>4</v>
       </c>
       <c r="G835" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H835" t="n">
         <v>4</v>
@@ -53033,10 +53033,10 @@
         <v>4</v>
       </c>
       <c r="J835" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K835" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L835" t="b">
         <v>0</v>
@@ -53060,7 +53060,7 @@
     <row r="836">
       <c r="A836" t="inlineStr">
         <is>
-          <t>p12</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="B836" t="inlineStr">
@@ -53123,7 +53123,7 @@
     <row r="837">
       <c r="A837" t="inlineStr">
         <is>
-          <t>p12</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="B837" t="inlineStr">
@@ -53186,7 +53186,7 @@
     <row r="838">
       <c r="A838" t="inlineStr">
         <is>
-          <t>p12</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="B838" t="inlineStr">
@@ -53249,7 +53249,7 @@
     <row r="839">
       <c r="A839" t="inlineStr">
         <is>
-          <t>p12</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="B839" t="inlineStr">
@@ -53312,7 +53312,7 @@
     <row r="840">
       <c r="A840" t="inlineStr">
         <is>
-          <t>p12</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="B840" t="inlineStr">
@@ -53336,7 +53336,7 @@
         </is>
       </c>
       <c r="F840" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G840" t="n">
         <v>4</v>
@@ -53351,7 +53351,7 @@
         <v>4</v>
       </c>
       <c r="K840" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L840" t="b">
         <v>0</v>
@@ -53375,7 +53375,7 @@
     <row r="841">
       <c r="A841" t="inlineStr">
         <is>
-          <t>p12</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="B841" t="inlineStr">
@@ -53438,7 +53438,7 @@
     <row r="842">
       <c r="A842" t="inlineStr">
         <is>
-          <t>p12</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="B842" t="inlineStr">
@@ -53501,7 +53501,7 @@
     <row r="843">
       <c r="A843" t="inlineStr">
         <is>
-          <t>p12</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="B843" t="inlineStr">
@@ -53528,19 +53528,19 @@
         <v>4</v>
       </c>
       <c r="G843" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H843" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I843" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J843" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K843" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="L843" t="b">
         <v>0</v>
@@ -53564,7 +53564,7 @@
     <row r="844">
       <c r="A844" t="inlineStr">
         <is>
-          <t>p12</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="B844" t="inlineStr">
@@ -53591,19 +53591,19 @@
         <v>4</v>
       </c>
       <c r="G844" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H844" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I844" t="n">
         <v>4</v>
       </c>
       <c r="J844" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K844" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L844" t="b">
         <v>0</v>
@@ -53627,7 +53627,7 @@
     <row r="845">
       <c r="A845" t="inlineStr">
         <is>
-          <t>p12</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="B845" t="inlineStr">
@@ -53663,10 +53663,10 @@
         <v>4</v>
       </c>
       <c r="J845" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K845" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L845" t="b">
         <v>0</v>
@@ -53690,7 +53690,7 @@
     <row r="846">
       <c r="A846" t="inlineStr">
         <is>
-          <t>p12</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="B846" t="inlineStr">
@@ -53753,7 +53753,7 @@
     <row r="847">
       <c r="A847" t="inlineStr">
         <is>
-          <t>p12</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="B847" t="inlineStr">
@@ -53777,22 +53777,22 @@
         </is>
       </c>
       <c r="F847" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G847" t="n">
         <v>3</v>
       </c>
       <c r="H847" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I847" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J847" t="n">
         <v>3</v>
       </c>
       <c r="K847" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="L847" t="b">
         <v>0</v>
@@ -53816,7 +53816,7 @@
     <row r="848">
       <c r="A848" t="inlineStr">
         <is>
-          <t>p12</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="B848" t="inlineStr">
@@ -53846,7 +53846,7 @@
         <v>4</v>
       </c>
       <c r="H848" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I848" t="n">
         <v>4</v>
@@ -53855,7 +53855,7 @@
         <v>4</v>
       </c>
       <c r="K848" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L848" t="b">
         <v>0</v>
@@ -53879,7 +53879,7 @@
     <row r="849">
       <c r="A849" t="inlineStr">
         <is>
-          <t>p12</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="B849" t="inlineStr">
@@ -53903,13 +53903,13 @@
         </is>
       </c>
       <c r="F849" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G849" t="n">
         <v>3</v>
       </c>
       <c r="H849" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I849" t="n">
         <v>3</v>
@@ -53918,7 +53918,7 @@
         <v>3</v>
       </c>
       <c r="K849" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L849" t="b">
         <v>0</v>
@@ -53942,7 +53942,7 @@
     <row r="850">
       <c r="A850" t="inlineStr">
         <is>
-          <t>p12</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="B850" t="inlineStr">
@@ -53966,22 +53966,22 @@
         </is>
       </c>
       <c r="F850" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G850" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H850" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I850" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J850" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K850" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="L850" t="b">
         <v>0</v>
@@ -54005,7 +54005,7 @@
     <row r="851">
       <c r="A851" t="inlineStr">
         <is>
-          <t>p12</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="B851" t="inlineStr">
@@ -54032,7 +54032,7 @@
         <v>4</v>
       </c>
       <c r="G851" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H851" t="n">
         <v>4</v>
@@ -54044,7 +54044,7 @@
         <v>4</v>
       </c>
       <c r="K851" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L851" t="b">
         <v>0</v>
@@ -54068,7 +54068,7 @@
     <row r="852">
       <c r="A852" t="inlineStr">
         <is>
-          <t>p12</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="B852" t="inlineStr">
@@ -54131,7 +54131,7 @@
     <row r="853">
       <c r="A853" t="inlineStr">
         <is>
-          <t>p12</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="B853" t="inlineStr">
@@ -54194,7 +54194,7 @@
     <row r="854">
       <c r="A854" t="inlineStr">
         <is>
-          <t>p12</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="B854" t="inlineStr">
@@ -54257,7 +54257,7 @@
     <row r="855">
       <c r="A855" t="inlineStr">
         <is>
-          <t>p12</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="B855" t="inlineStr">
@@ -54284,7 +54284,7 @@
         <v>4</v>
       </c>
       <c r="G855" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H855" t="n">
         <v>4</v>
@@ -54296,7 +54296,7 @@
         <v>4</v>
       </c>
       <c r="K855" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L855" t="b">
         <v>0</v>
@@ -54320,7 +54320,7 @@
     <row r="856">
       <c r="A856" t="inlineStr">
         <is>
-          <t>p12</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="B856" t="inlineStr">
@@ -54383,7 +54383,7 @@
     <row r="857">
       <c r="A857" t="inlineStr">
         <is>
-          <t>p12</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="B857" t="inlineStr">
@@ -54446,7 +54446,7 @@
     <row r="858">
       <c r="A858" t="inlineStr">
         <is>
-          <t>p12</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="B858" t="inlineStr">
@@ -54482,10 +54482,10 @@
         <v>4</v>
       </c>
       <c r="J858" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K858" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L858" t="b">
         <v>0</v>
@@ -54509,7 +54509,7 @@
     <row r="859">
       <c r="A859" t="inlineStr">
         <is>
-          <t>p12</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="B859" t="inlineStr">
@@ -54536,19 +54536,19 @@
         <v>4</v>
       </c>
       <c r="G859" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H859" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I859" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J859" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K859" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L859" t="b">
         <v>0</v>
@@ -54572,7 +54572,7 @@
     <row r="860">
       <c r="A860" t="inlineStr">
         <is>
-          <t>p12</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="B860" t="inlineStr">
@@ -54635,7 +54635,7 @@
     <row r="861">
       <c r="A861" t="inlineStr">
         <is>
-          <t>p12</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="B861" t="inlineStr">
@@ -54662,19 +54662,19 @@
         <v>4</v>
       </c>
       <c r="G861" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H861" t="n">
         <v>4</v>
       </c>
       <c r="I861" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J861" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K861" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L861" t="b">
         <v>0</v>
@@ -54698,7 +54698,7 @@
     <row r="862">
       <c r="A862" t="inlineStr">
         <is>
-          <t>p12</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="B862" t="inlineStr">
@@ -54761,7 +54761,7 @@
     <row r="863">
       <c r="A863" t="inlineStr">
         <is>
-          <t>p12</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="B863" t="inlineStr">
@@ -54818,6 +54818,4542 @@
         <v>0</v>
       </c>
       <c r="Q863" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" t="inlineStr">
+        <is>
+          <t>p12</t>
+        </is>
+      </c>
+      <c r="B864" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C864" t="inlineStr">
+        <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="D864" t="inlineStr">
+        <is>
+          <t>chatgpt</t>
+        </is>
+      </c>
+      <c r="E864" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="F864" t="n">
+        <v>4</v>
+      </c>
+      <c r="G864" t="n">
+        <v>4</v>
+      </c>
+      <c r="H864" t="n">
+        <v>3</v>
+      </c>
+      <c r="I864" t="n">
+        <v>4</v>
+      </c>
+      <c r="J864" t="n">
+        <v>4</v>
+      </c>
+      <c r="K864" t="n">
+        <v>19</v>
+      </c>
+      <c r="L864" t="b">
+        <v>0</v>
+      </c>
+      <c r="M864" t="b">
+        <v>0</v>
+      </c>
+      <c r="N864" t="b">
+        <v>0</v>
+      </c>
+      <c r="O864" t="b">
+        <v>0</v>
+      </c>
+      <c r="P864" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q864" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" t="inlineStr">
+        <is>
+          <t>p12</t>
+        </is>
+      </c>
+      <c r="B865" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C865" t="inlineStr">
+        <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="D865" t="inlineStr">
+        <is>
+          <t>chatgpt</t>
+        </is>
+      </c>
+      <c r="E865" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="F865" t="n">
+        <v>4</v>
+      </c>
+      <c r="G865" t="n">
+        <v>4</v>
+      </c>
+      <c r="H865" t="n">
+        <v>4</v>
+      </c>
+      <c r="I865" t="n">
+        <v>4</v>
+      </c>
+      <c r="J865" t="n">
+        <v>4</v>
+      </c>
+      <c r="K865" t="n">
+        <v>20</v>
+      </c>
+      <c r="L865" t="b">
+        <v>0</v>
+      </c>
+      <c r="M865" t="b">
+        <v>0</v>
+      </c>
+      <c r="N865" t="b">
+        <v>0</v>
+      </c>
+      <c r="O865" t="b">
+        <v>0</v>
+      </c>
+      <c r="P865" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q865" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" t="inlineStr">
+        <is>
+          <t>p12</t>
+        </is>
+      </c>
+      <c r="B866" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C866" t="inlineStr">
+        <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="D866" t="inlineStr">
+        <is>
+          <t>chatgpt</t>
+        </is>
+      </c>
+      <c r="E866" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="F866" t="n">
+        <v>4</v>
+      </c>
+      <c r="G866" t="n">
+        <v>4</v>
+      </c>
+      <c r="H866" t="n">
+        <v>4</v>
+      </c>
+      <c r="I866" t="n">
+        <v>4</v>
+      </c>
+      <c r="J866" t="n">
+        <v>4</v>
+      </c>
+      <c r="K866" t="n">
+        <v>20</v>
+      </c>
+      <c r="L866" t="b">
+        <v>0</v>
+      </c>
+      <c r="M866" t="b">
+        <v>0</v>
+      </c>
+      <c r="N866" t="b">
+        <v>0</v>
+      </c>
+      <c r="O866" t="b">
+        <v>0</v>
+      </c>
+      <c r="P866" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q866" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" t="inlineStr">
+        <is>
+          <t>p12</t>
+        </is>
+      </c>
+      <c r="B867" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C867" t="inlineStr">
+        <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="D867" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="E867" t="inlineStr">
+        <is>
+          <t>chatgpt</t>
+        </is>
+      </c>
+      <c r="F867" t="n">
+        <v>4</v>
+      </c>
+      <c r="G867" t="n">
+        <v>3</v>
+      </c>
+      <c r="H867" t="n">
+        <v>3</v>
+      </c>
+      <c r="I867" t="n">
+        <v>3</v>
+      </c>
+      <c r="J867" t="n">
+        <v>2</v>
+      </c>
+      <c r="K867" t="n">
+        <v>15</v>
+      </c>
+      <c r="L867" t="b">
+        <v>0</v>
+      </c>
+      <c r="M867" t="b">
+        <v>0</v>
+      </c>
+      <c r="N867" t="b">
+        <v>0</v>
+      </c>
+      <c r="O867" t="b">
+        <v>0</v>
+      </c>
+      <c r="P867" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q867" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" t="inlineStr">
+        <is>
+          <t>p12</t>
+        </is>
+      </c>
+      <c r="B868" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C868" t="inlineStr">
+        <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="D868" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="E868" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="F868" t="n">
+        <v>4</v>
+      </c>
+      <c r="G868" t="n">
+        <v>4</v>
+      </c>
+      <c r="H868" t="n">
+        <v>4</v>
+      </c>
+      <c r="I868" t="n">
+        <v>4</v>
+      </c>
+      <c r="J868" t="n">
+        <v>4</v>
+      </c>
+      <c r="K868" t="n">
+        <v>20</v>
+      </c>
+      <c r="L868" t="b">
+        <v>0</v>
+      </c>
+      <c r="M868" t="b">
+        <v>0</v>
+      </c>
+      <c r="N868" t="b">
+        <v>0</v>
+      </c>
+      <c r="O868" t="b">
+        <v>0</v>
+      </c>
+      <c r="P868" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q868" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" t="inlineStr">
+        <is>
+          <t>p12</t>
+        </is>
+      </c>
+      <c r="B869" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C869" t="inlineStr">
+        <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="D869" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="E869" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="F869" t="n">
+        <v>4</v>
+      </c>
+      <c r="G869" t="n">
+        <v>4</v>
+      </c>
+      <c r="H869" t="n">
+        <v>4</v>
+      </c>
+      <c r="I869" t="n">
+        <v>4</v>
+      </c>
+      <c r="J869" t="n">
+        <v>3</v>
+      </c>
+      <c r="K869" t="n">
+        <v>19</v>
+      </c>
+      <c r="L869" t="b">
+        <v>0</v>
+      </c>
+      <c r="M869" t="b">
+        <v>0</v>
+      </c>
+      <c r="N869" t="b">
+        <v>0</v>
+      </c>
+      <c r="O869" t="b">
+        <v>0</v>
+      </c>
+      <c r="P869" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q869" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" t="inlineStr">
+        <is>
+          <t>p12</t>
+        </is>
+      </c>
+      <c r="B870" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C870" t="inlineStr">
+        <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="D870" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="E870" t="inlineStr">
+        <is>
+          <t>chatgpt</t>
+        </is>
+      </c>
+      <c r="F870" t="n">
+        <v>4</v>
+      </c>
+      <c r="G870" t="n">
+        <v>3</v>
+      </c>
+      <c r="H870" t="n">
+        <v>3</v>
+      </c>
+      <c r="I870" t="n">
+        <v>4</v>
+      </c>
+      <c r="J870" t="n">
+        <v>3</v>
+      </c>
+      <c r="K870" t="n">
+        <v>17</v>
+      </c>
+      <c r="L870" t="b">
+        <v>0</v>
+      </c>
+      <c r="M870" t="b">
+        <v>0</v>
+      </c>
+      <c r="N870" t="b">
+        <v>0</v>
+      </c>
+      <c r="O870" t="b">
+        <v>0</v>
+      </c>
+      <c r="P870" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q870" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="inlineStr">
+        <is>
+          <t>p12</t>
+        </is>
+      </c>
+      <c r="B871" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C871" t="inlineStr">
+        <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="D871" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="E871" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="F871" t="n">
+        <v>4</v>
+      </c>
+      <c r="G871" t="n">
+        <v>4</v>
+      </c>
+      <c r="H871" t="n">
+        <v>3</v>
+      </c>
+      <c r="I871" t="n">
+        <v>4</v>
+      </c>
+      <c r="J871" t="n">
+        <v>4</v>
+      </c>
+      <c r="K871" t="n">
+        <v>19</v>
+      </c>
+      <c r="L871" t="b">
+        <v>0</v>
+      </c>
+      <c r="M871" t="b">
+        <v>0</v>
+      </c>
+      <c r="N871" t="b">
+        <v>0</v>
+      </c>
+      <c r="O871" t="b">
+        <v>0</v>
+      </c>
+      <c r="P871" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q871" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="inlineStr">
+        <is>
+          <t>p12</t>
+        </is>
+      </c>
+      <c r="B872" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C872" t="inlineStr">
+        <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="D872" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="E872" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="F872" t="n">
+        <v>4</v>
+      </c>
+      <c r="G872" t="n">
+        <v>4</v>
+      </c>
+      <c r="H872" t="n">
+        <v>4</v>
+      </c>
+      <c r="I872" t="n">
+        <v>4</v>
+      </c>
+      <c r="J872" t="n">
+        <v>4</v>
+      </c>
+      <c r="K872" t="n">
+        <v>20</v>
+      </c>
+      <c r="L872" t="b">
+        <v>0</v>
+      </c>
+      <c r="M872" t="b">
+        <v>0</v>
+      </c>
+      <c r="N872" t="b">
+        <v>0</v>
+      </c>
+      <c r="O872" t="b">
+        <v>0</v>
+      </c>
+      <c r="P872" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q872" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" t="inlineStr">
+        <is>
+          <t>p12</t>
+        </is>
+      </c>
+      <c r="B873" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C873" t="inlineStr">
+        <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="D873" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="E873" t="inlineStr">
+        <is>
+          <t>chatgpt</t>
+        </is>
+      </c>
+      <c r="F873" t="n">
+        <v>4</v>
+      </c>
+      <c r="G873" t="n">
+        <v>3</v>
+      </c>
+      <c r="H873" t="n">
+        <v>3</v>
+      </c>
+      <c r="I873" t="n">
+        <v>3</v>
+      </c>
+      <c r="J873" t="n">
+        <v>3</v>
+      </c>
+      <c r="K873" t="n">
+        <v>16</v>
+      </c>
+      <c r="L873" t="b">
+        <v>0</v>
+      </c>
+      <c r="M873" t="b">
+        <v>0</v>
+      </c>
+      <c r="N873" t="b">
+        <v>0</v>
+      </c>
+      <c r="O873" t="b">
+        <v>0</v>
+      </c>
+      <c r="P873" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q873" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" t="inlineStr">
+        <is>
+          <t>p12</t>
+        </is>
+      </c>
+      <c r="B874" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C874" t="inlineStr">
+        <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="D874" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="E874" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="F874" t="n">
+        <v>4</v>
+      </c>
+      <c r="G874" t="n">
+        <v>4</v>
+      </c>
+      <c r="H874" t="n">
+        <v>3</v>
+      </c>
+      <c r="I874" t="n">
+        <v>4</v>
+      </c>
+      <c r="J874" t="n">
+        <v>4</v>
+      </c>
+      <c r="K874" t="n">
+        <v>19</v>
+      </c>
+      <c r="L874" t="b">
+        <v>0</v>
+      </c>
+      <c r="M874" t="b">
+        <v>0</v>
+      </c>
+      <c r="N874" t="b">
+        <v>0</v>
+      </c>
+      <c r="O874" t="b">
+        <v>0</v>
+      </c>
+      <c r="P874" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q874" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" t="inlineStr">
+        <is>
+          <t>p12</t>
+        </is>
+      </c>
+      <c r="B875" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C875" t="inlineStr">
+        <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="D875" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="E875" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="F875" t="n">
+        <v>4</v>
+      </c>
+      <c r="G875" t="n">
+        <v>4</v>
+      </c>
+      <c r="H875" t="n">
+        <v>4</v>
+      </c>
+      <c r="I875" t="n">
+        <v>4</v>
+      </c>
+      <c r="J875" t="n">
+        <v>4</v>
+      </c>
+      <c r="K875" t="n">
+        <v>20</v>
+      </c>
+      <c r="L875" t="b">
+        <v>0</v>
+      </c>
+      <c r="M875" t="b">
+        <v>0</v>
+      </c>
+      <c r="N875" t="b">
+        <v>0</v>
+      </c>
+      <c r="O875" t="b">
+        <v>0</v>
+      </c>
+      <c r="P875" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q875" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" t="inlineStr">
+        <is>
+          <t>p12</t>
+        </is>
+      </c>
+      <c r="B876" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C876" t="inlineStr">
+        <is>
+          <t>tune</t>
+        </is>
+      </c>
+      <c r="D876" t="inlineStr">
+        <is>
+          <t>chatgpt</t>
+        </is>
+      </c>
+      <c r="E876" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="F876" t="n">
+        <v>4</v>
+      </c>
+      <c r="G876" t="n">
+        <v>4</v>
+      </c>
+      <c r="H876" t="n">
+        <v>4</v>
+      </c>
+      <c r="I876" t="n">
+        <v>4</v>
+      </c>
+      <c r="J876" t="n">
+        <v>4</v>
+      </c>
+      <c r="K876" t="n">
+        <v>20</v>
+      </c>
+      <c r="L876" t="b">
+        <v>0</v>
+      </c>
+      <c r="M876" t="b">
+        <v>0</v>
+      </c>
+      <c r="N876" t="b">
+        <v>0</v>
+      </c>
+      <c r="O876" t="b">
+        <v>0</v>
+      </c>
+      <c r="P876" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q876" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" t="inlineStr">
+        <is>
+          <t>p12</t>
+        </is>
+      </c>
+      <c r="B877" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C877" t="inlineStr">
+        <is>
+          <t>tune</t>
+        </is>
+      </c>
+      <c r="D877" t="inlineStr">
+        <is>
+          <t>chatgpt</t>
+        </is>
+      </c>
+      <c r="E877" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="F877" t="n">
+        <v>4</v>
+      </c>
+      <c r="G877" t="n">
+        <v>4</v>
+      </c>
+      <c r="H877" t="n">
+        <v>4</v>
+      </c>
+      <c r="I877" t="n">
+        <v>4</v>
+      </c>
+      <c r="J877" t="n">
+        <v>4</v>
+      </c>
+      <c r="K877" t="n">
+        <v>20</v>
+      </c>
+      <c r="L877" t="b">
+        <v>0</v>
+      </c>
+      <c r="M877" t="b">
+        <v>0</v>
+      </c>
+      <c r="N877" t="b">
+        <v>0</v>
+      </c>
+      <c r="O877" t="b">
+        <v>0</v>
+      </c>
+      <c r="P877" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q877" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" t="inlineStr">
+        <is>
+          <t>p12</t>
+        </is>
+      </c>
+      <c r="B878" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C878" t="inlineStr">
+        <is>
+          <t>tune</t>
+        </is>
+      </c>
+      <c r="D878" t="inlineStr">
+        <is>
+          <t>chatgpt</t>
+        </is>
+      </c>
+      <c r="E878" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="F878" t="n">
+        <v>4</v>
+      </c>
+      <c r="G878" t="n">
+        <v>4</v>
+      </c>
+      <c r="H878" t="n">
+        <v>4</v>
+      </c>
+      <c r="I878" t="n">
+        <v>4</v>
+      </c>
+      <c r="J878" t="n">
+        <v>4</v>
+      </c>
+      <c r="K878" t="n">
+        <v>20</v>
+      </c>
+      <c r="L878" t="b">
+        <v>0</v>
+      </c>
+      <c r="M878" t="b">
+        <v>0</v>
+      </c>
+      <c r="N878" t="b">
+        <v>0</v>
+      </c>
+      <c r="O878" t="b">
+        <v>0</v>
+      </c>
+      <c r="P878" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q878" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" t="inlineStr">
+        <is>
+          <t>p12</t>
+        </is>
+      </c>
+      <c r="B879" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C879" t="inlineStr">
+        <is>
+          <t>tune</t>
+        </is>
+      </c>
+      <c r="D879" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="E879" t="inlineStr">
+        <is>
+          <t>chatgpt</t>
+        </is>
+      </c>
+      <c r="F879" t="n">
+        <v>4</v>
+      </c>
+      <c r="G879" t="n">
+        <v>3</v>
+      </c>
+      <c r="H879" t="n">
+        <v>4</v>
+      </c>
+      <c r="I879" t="n">
+        <v>4</v>
+      </c>
+      <c r="J879" t="n">
+        <v>3</v>
+      </c>
+      <c r="K879" t="n">
+        <v>18</v>
+      </c>
+      <c r="L879" t="b">
+        <v>0</v>
+      </c>
+      <c r="M879" t="b">
+        <v>0</v>
+      </c>
+      <c r="N879" t="b">
+        <v>0</v>
+      </c>
+      <c r="O879" t="b">
+        <v>0</v>
+      </c>
+      <c r="P879" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q879" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" t="inlineStr">
+        <is>
+          <t>p12</t>
+        </is>
+      </c>
+      <c r="B880" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C880" t="inlineStr">
+        <is>
+          <t>tune</t>
+        </is>
+      </c>
+      <c r="D880" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="E880" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="F880" t="n">
+        <v>4</v>
+      </c>
+      <c r="G880" t="n">
+        <v>4</v>
+      </c>
+      <c r="H880" t="n">
+        <v>4</v>
+      </c>
+      <c r="I880" t="n">
+        <v>4</v>
+      </c>
+      <c r="J880" t="n">
+        <v>4</v>
+      </c>
+      <c r="K880" t="n">
+        <v>20</v>
+      </c>
+      <c r="L880" t="b">
+        <v>0</v>
+      </c>
+      <c r="M880" t="b">
+        <v>0</v>
+      </c>
+      <c r="N880" t="b">
+        <v>0</v>
+      </c>
+      <c r="O880" t="b">
+        <v>0</v>
+      </c>
+      <c r="P880" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q880" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" t="inlineStr">
+        <is>
+          <t>p12</t>
+        </is>
+      </c>
+      <c r="B881" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C881" t="inlineStr">
+        <is>
+          <t>tune</t>
+        </is>
+      </c>
+      <c r="D881" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="E881" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="F881" t="n">
+        <v>4</v>
+      </c>
+      <c r="G881" t="n">
+        <v>4</v>
+      </c>
+      <c r="H881" t="n">
+        <v>4</v>
+      </c>
+      <c r="I881" t="n">
+        <v>4</v>
+      </c>
+      <c r="J881" t="n">
+        <v>4</v>
+      </c>
+      <c r="K881" t="n">
+        <v>20</v>
+      </c>
+      <c r="L881" t="b">
+        <v>0</v>
+      </c>
+      <c r="M881" t="b">
+        <v>0</v>
+      </c>
+      <c r="N881" t="b">
+        <v>0</v>
+      </c>
+      <c r="O881" t="b">
+        <v>0</v>
+      </c>
+      <c r="P881" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q881" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" t="inlineStr">
+        <is>
+          <t>p12</t>
+        </is>
+      </c>
+      <c r="B882" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C882" t="inlineStr">
+        <is>
+          <t>tune</t>
+        </is>
+      </c>
+      <c r="D882" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="E882" t="inlineStr">
+        <is>
+          <t>chatgpt</t>
+        </is>
+      </c>
+      <c r="F882" t="n">
+        <v>4</v>
+      </c>
+      <c r="G882" t="n">
+        <v>3</v>
+      </c>
+      <c r="H882" t="n">
+        <v>4</v>
+      </c>
+      <c r="I882" t="n">
+        <v>4</v>
+      </c>
+      <c r="J882" t="n">
+        <v>3</v>
+      </c>
+      <c r="K882" t="n">
+        <v>18</v>
+      </c>
+      <c r="L882" t="b">
+        <v>0</v>
+      </c>
+      <c r="M882" t="b">
+        <v>0</v>
+      </c>
+      <c r="N882" t="b">
+        <v>0</v>
+      </c>
+      <c r="O882" t="b">
+        <v>0</v>
+      </c>
+      <c r="P882" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q882" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" t="inlineStr">
+        <is>
+          <t>p12</t>
+        </is>
+      </c>
+      <c r="B883" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C883" t="inlineStr">
+        <is>
+          <t>tune</t>
+        </is>
+      </c>
+      <c r="D883" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="E883" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="F883" t="n">
+        <v>4</v>
+      </c>
+      <c r="G883" t="n">
+        <v>4</v>
+      </c>
+      <c r="H883" t="n">
+        <v>4</v>
+      </c>
+      <c r="I883" t="n">
+        <v>4</v>
+      </c>
+      <c r="J883" t="n">
+        <v>4</v>
+      </c>
+      <c r="K883" t="n">
+        <v>20</v>
+      </c>
+      <c r="L883" t="b">
+        <v>0</v>
+      </c>
+      <c r="M883" t="b">
+        <v>0</v>
+      </c>
+      <c r="N883" t="b">
+        <v>0</v>
+      </c>
+      <c r="O883" t="b">
+        <v>0</v>
+      </c>
+      <c r="P883" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q883" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" t="inlineStr">
+        <is>
+          <t>p12</t>
+        </is>
+      </c>
+      <c r="B884" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C884" t="inlineStr">
+        <is>
+          <t>tune</t>
+        </is>
+      </c>
+      <c r="D884" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="E884" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="F884" t="n">
+        <v>4</v>
+      </c>
+      <c r="G884" t="n">
+        <v>4</v>
+      </c>
+      <c r="H884" t="n">
+        <v>4</v>
+      </c>
+      <c r="I884" t="n">
+        <v>4</v>
+      </c>
+      <c r="J884" t="n">
+        <v>4</v>
+      </c>
+      <c r="K884" t="n">
+        <v>20</v>
+      </c>
+      <c r="L884" t="b">
+        <v>0</v>
+      </c>
+      <c r="M884" t="b">
+        <v>0</v>
+      </c>
+      <c r="N884" t="b">
+        <v>0</v>
+      </c>
+      <c r="O884" t="b">
+        <v>0</v>
+      </c>
+      <c r="P884" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q884" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" t="inlineStr">
+        <is>
+          <t>p12</t>
+        </is>
+      </c>
+      <c r="B885" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C885" t="inlineStr">
+        <is>
+          <t>tune</t>
+        </is>
+      </c>
+      <c r="D885" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="E885" t="inlineStr">
+        <is>
+          <t>chatgpt</t>
+        </is>
+      </c>
+      <c r="F885" t="n">
+        <v>4</v>
+      </c>
+      <c r="G885" t="n">
+        <v>3</v>
+      </c>
+      <c r="H885" t="n">
+        <v>4</v>
+      </c>
+      <c r="I885" t="n">
+        <v>4</v>
+      </c>
+      <c r="J885" t="n">
+        <v>3</v>
+      </c>
+      <c r="K885" t="n">
+        <v>18</v>
+      </c>
+      <c r="L885" t="b">
+        <v>0</v>
+      </c>
+      <c r="M885" t="b">
+        <v>0</v>
+      </c>
+      <c r="N885" t="b">
+        <v>0</v>
+      </c>
+      <c r="O885" t="b">
+        <v>0</v>
+      </c>
+      <c r="P885" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q885" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" t="inlineStr">
+        <is>
+          <t>p12</t>
+        </is>
+      </c>
+      <c r="B886" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C886" t="inlineStr">
+        <is>
+          <t>tune</t>
+        </is>
+      </c>
+      <c r="D886" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="E886" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="F886" t="n">
+        <v>4</v>
+      </c>
+      <c r="G886" t="n">
+        <v>4</v>
+      </c>
+      <c r="H886" t="n">
+        <v>4</v>
+      </c>
+      <c r="I886" t="n">
+        <v>4</v>
+      </c>
+      <c r="J886" t="n">
+        <v>4</v>
+      </c>
+      <c r="K886" t="n">
+        <v>20</v>
+      </c>
+      <c r="L886" t="b">
+        <v>0</v>
+      </c>
+      <c r="M886" t="b">
+        <v>0</v>
+      </c>
+      <c r="N886" t="b">
+        <v>0</v>
+      </c>
+      <c r="O886" t="b">
+        <v>0</v>
+      </c>
+      <c r="P886" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q886" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" t="inlineStr">
+        <is>
+          <t>p12</t>
+        </is>
+      </c>
+      <c r="B887" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C887" t="inlineStr">
+        <is>
+          <t>tune</t>
+        </is>
+      </c>
+      <c r="D887" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="E887" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="F887" t="n">
+        <v>4</v>
+      </c>
+      <c r="G887" t="n">
+        <v>4</v>
+      </c>
+      <c r="H887" t="n">
+        <v>4</v>
+      </c>
+      <c r="I887" t="n">
+        <v>4</v>
+      </c>
+      <c r="J887" t="n">
+        <v>4</v>
+      </c>
+      <c r="K887" t="n">
+        <v>20</v>
+      </c>
+      <c r="L887" t="b">
+        <v>0</v>
+      </c>
+      <c r="M887" t="b">
+        <v>0</v>
+      </c>
+      <c r="N887" t="b">
+        <v>0</v>
+      </c>
+      <c r="O887" t="b">
+        <v>0</v>
+      </c>
+      <c r="P887" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q887" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" t="inlineStr">
+        <is>
+          <t>p12</t>
+        </is>
+      </c>
+      <c r="B888" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C888" t="inlineStr">
+        <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="D888" t="inlineStr">
+        <is>
+          <t>chatgpt</t>
+        </is>
+      </c>
+      <c r="E888" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="F888" t="n">
+        <v>4</v>
+      </c>
+      <c r="G888" t="n">
+        <v>4</v>
+      </c>
+      <c r="H888" t="n">
+        <v>4</v>
+      </c>
+      <c r="I888" t="n">
+        <v>4</v>
+      </c>
+      <c r="J888" t="n">
+        <v>4</v>
+      </c>
+      <c r="K888" t="n">
+        <v>20</v>
+      </c>
+      <c r="L888" t="b">
+        <v>0</v>
+      </c>
+      <c r="M888" t="b">
+        <v>0</v>
+      </c>
+      <c r="N888" t="b">
+        <v>0</v>
+      </c>
+      <c r="O888" t="b">
+        <v>0</v>
+      </c>
+      <c r="P888" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q888" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" t="inlineStr">
+        <is>
+          <t>p12</t>
+        </is>
+      </c>
+      <c r="B889" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C889" t="inlineStr">
+        <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="D889" t="inlineStr">
+        <is>
+          <t>chatgpt</t>
+        </is>
+      </c>
+      <c r="E889" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="F889" t="n">
+        <v>4</v>
+      </c>
+      <c r="G889" t="n">
+        <v>4</v>
+      </c>
+      <c r="H889" t="n">
+        <v>4</v>
+      </c>
+      <c r="I889" t="n">
+        <v>4</v>
+      </c>
+      <c r="J889" t="n">
+        <v>4</v>
+      </c>
+      <c r="K889" t="n">
+        <v>20</v>
+      </c>
+      <c r="L889" t="b">
+        <v>0</v>
+      </c>
+      <c r="M889" t="b">
+        <v>0</v>
+      </c>
+      <c r="N889" t="b">
+        <v>0</v>
+      </c>
+      <c r="O889" t="b">
+        <v>0</v>
+      </c>
+      <c r="P889" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q889" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" t="inlineStr">
+        <is>
+          <t>p12</t>
+        </is>
+      </c>
+      <c r="B890" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C890" t="inlineStr">
+        <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="D890" t="inlineStr">
+        <is>
+          <t>chatgpt</t>
+        </is>
+      </c>
+      <c r="E890" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="F890" t="n">
+        <v>4</v>
+      </c>
+      <c r="G890" t="n">
+        <v>4</v>
+      </c>
+      <c r="H890" t="n">
+        <v>4</v>
+      </c>
+      <c r="I890" t="n">
+        <v>4</v>
+      </c>
+      <c r="J890" t="n">
+        <v>4</v>
+      </c>
+      <c r="K890" t="n">
+        <v>20</v>
+      </c>
+      <c r="L890" t="b">
+        <v>0</v>
+      </c>
+      <c r="M890" t="b">
+        <v>0</v>
+      </c>
+      <c r="N890" t="b">
+        <v>0</v>
+      </c>
+      <c r="O890" t="b">
+        <v>0</v>
+      </c>
+      <c r="P890" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q890" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" t="inlineStr">
+        <is>
+          <t>p12</t>
+        </is>
+      </c>
+      <c r="B891" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C891" t="inlineStr">
+        <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="D891" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="E891" t="inlineStr">
+        <is>
+          <t>chatgpt</t>
+        </is>
+      </c>
+      <c r="F891" t="n">
+        <v>4</v>
+      </c>
+      <c r="G891" t="n">
+        <v>3</v>
+      </c>
+      <c r="H891" t="n">
+        <v>4</v>
+      </c>
+      <c r="I891" t="n">
+        <v>3</v>
+      </c>
+      <c r="J891" t="n">
+        <v>3</v>
+      </c>
+      <c r="K891" t="n">
+        <v>17</v>
+      </c>
+      <c r="L891" t="b">
+        <v>0</v>
+      </c>
+      <c r="M891" t="b">
+        <v>0</v>
+      </c>
+      <c r="N891" t="b">
+        <v>0</v>
+      </c>
+      <c r="O891" t="b">
+        <v>0</v>
+      </c>
+      <c r="P891" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q891" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" t="inlineStr">
+        <is>
+          <t>p12</t>
+        </is>
+      </c>
+      <c r="B892" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C892" t="inlineStr">
+        <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="D892" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="E892" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="F892" t="n">
+        <v>4</v>
+      </c>
+      <c r="G892" t="n">
+        <v>4</v>
+      </c>
+      <c r="H892" t="n">
+        <v>4</v>
+      </c>
+      <c r="I892" t="n">
+        <v>4</v>
+      </c>
+      <c r="J892" t="n">
+        <v>3</v>
+      </c>
+      <c r="K892" t="n">
+        <v>19</v>
+      </c>
+      <c r="L892" t="b">
+        <v>0</v>
+      </c>
+      <c r="M892" t="b">
+        <v>0</v>
+      </c>
+      <c r="N892" t="b">
+        <v>0</v>
+      </c>
+      <c r="O892" t="b">
+        <v>0</v>
+      </c>
+      <c r="P892" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q892" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" t="inlineStr">
+        <is>
+          <t>p12</t>
+        </is>
+      </c>
+      <c r="B893" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C893" t="inlineStr">
+        <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="D893" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="E893" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="F893" t="n">
+        <v>4</v>
+      </c>
+      <c r="G893" t="n">
+        <v>4</v>
+      </c>
+      <c r="H893" t="n">
+        <v>4</v>
+      </c>
+      <c r="I893" t="n">
+        <v>4</v>
+      </c>
+      <c r="J893" t="n">
+        <v>4</v>
+      </c>
+      <c r="K893" t="n">
+        <v>20</v>
+      </c>
+      <c r="L893" t="b">
+        <v>0</v>
+      </c>
+      <c r="M893" t="b">
+        <v>0</v>
+      </c>
+      <c r="N893" t="b">
+        <v>0</v>
+      </c>
+      <c r="O893" t="b">
+        <v>0</v>
+      </c>
+      <c r="P893" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q893" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" t="inlineStr">
+        <is>
+          <t>p12</t>
+        </is>
+      </c>
+      <c r="B894" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C894" t="inlineStr">
+        <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="D894" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="E894" t="inlineStr">
+        <is>
+          <t>chatgpt</t>
+        </is>
+      </c>
+      <c r="F894" t="n">
+        <v>4</v>
+      </c>
+      <c r="G894" t="n">
+        <v>3</v>
+      </c>
+      <c r="H894" t="n">
+        <v>3</v>
+      </c>
+      <c r="I894" t="n">
+        <v>4</v>
+      </c>
+      <c r="J894" t="n">
+        <v>3</v>
+      </c>
+      <c r="K894" t="n">
+        <v>17</v>
+      </c>
+      <c r="L894" t="b">
+        <v>0</v>
+      </c>
+      <c r="M894" t="b">
+        <v>0</v>
+      </c>
+      <c r="N894" t="b">
+        <v>0</v>
+      </c>
+      <c r="O894" t="b">
+        <v>0</v>
+      </c>
+      <c r="P894" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q894" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" t="inlineStr">
+        <is>
+          <t>p12</t>
+        </is>
+      </c>
+      <c r="B895" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C895" t="inlineStr">
+        <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="D895" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="E895" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="F895" t="n">
+        <v>4</v>
+      </c>
+      <c r="G895" t="n">
+        <v>4</v>
+      </c>
+      <c r="H895" t="n">
+        <v>4</v>
+      </c>
+      <c r="I895" t="n">
+        <v>4</v>
+      </c>
+      <c r="J895" t="n">
+        <v>3</v>
+      </c>
+      <c r="K895" t="n">
+        <v>19</v>
+      </c>
+      <c r="L895" t="b">
+        <v>0</v>
+      </c>
+      <c r="M895" t="b">
+        <v>0</v>
+      </c>
+      <c r="N895" t="b">
+        <v>0</v>
+      </c>
+      <c r="O895" t="b">
+        <v>0</v>
+      </c>
+      <c r="P895" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q895" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" t="inlineStr">
+        <is>
+          <t>p12</t>
+        </is>
+      </c>
+      <c r="B896" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C896" t="inlineStr">
+        <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="D896" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="E896" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="F896" t="n">
+        <v>4</v>
+      </c>
+      <c r="G896" t="n">
+        <v>4</v>
+      </c>
+      <c r="H896" t="n">
+        <v>4</v>
+      </c>
+      <c r="I896" t="n">
+        <v>4</v>
+      </c>
+      <c r="J896" t="n">
+        <v>4</v>
+      </c>
+      <c r="K896" t="n">
+        <v>20</v>
+      </c>
+      <c r="L896" t="b">
+        <v>0</v>
+      </c>
+      <c r="M896" t="b">
+        <v>0</v>
+      </c>
+      <c r="N896" t="b">
+        <v>0</v>
+      </c>
+      <c r="O896" t="b">
+        <v>0</v>
+      </c>
+      <c r="P896" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q896" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" t="inlineStr">
+        <is>
+          <t>p12</t>
+        </is>
+      </c>
+      <c r="B897" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C897" t="inlineStr">
+        <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="D897" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="E897" t="inlineStr">
+        <is>
+          <t>chatgpt</t>
+        </is>
+      </c>
+      <c r="F897" t="n">
+        <v>4</v>
+      </c>
+      <c r="G897" t="n">
+        <v>3</v>
+      </c>
+      <c r="H897" t="n">
+        <v>3</v>
+      </c>
+      <c r="I897" t="n">
+        <v>3</v>
+      </c>
+      <c r="J897" t="n">
+        <v>3</v>
+      </c>
+      <c r="K897" t="n">
+        <v>16</v>
+      </c>
+      <c r="L897" t="b">
+        <v>0</v>
+      </c>
+      <c r="M897" t="b">
+        <v>0</v>
+      </c>
+      <c r="N897" t="b">
+        <v>0</v>
+      </c>
+      <c r="O897" t="b">
+        <v>0</v>
+      </c>
+      <c r="P897" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q897" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" t="inlineStr">
+        <is>
+          <t>p12</t>
+        </is>
+      </c>
+      <c r="B898" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C898" t="inlineStr">
+        <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="D898" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="E898" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="F898" t="n">
+        <v>4</v>
+      </c>
+      <c r="G898" t="n">
+        <v>4</v>
+      </c>
+      <c r="H898" t="n">
+        <v>3</v>
+      </c>
+      <c r="I898" t="n">
+        <v>4</v>
+      </c>
+      <c r="J898" t="n">
+        <v>3</v>
+      </c>
+      <c r="K898" t="n">
+        <v>18</v>
+      </c>
+      <c r="L898" t="b">
+        <v>0</v>
+      </c>
+      <c r="M898" t="b">
+        <v>0</v>
+      </c>
+      <c r="N898" t="b">
+        <v>0</v>
+      </c>
+      <c r="O898" t="b">
+        <v>0</v>
+      </c>
+      <c r="P898" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q898" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" t="inlineStr">
+        <is>
+          <t>p12</t>
+        </is>
+      </c>
+      <c r="B899" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C899" t="inlineStr">
+        <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="D899" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="E899" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="F899" t="n">
+        <v>4</v>
+      </c>
+      <c r="G899" t="n">
+        <v>4</v>
+      </c>
+      <c r="H899" t="n">
+        <v>4</v>
+      </c>
+      <c r="I899" t="n">
+        <v>4</v>
+      </c>
+      <c r="J899" t="n">
+        <v>4</v>
+      </c>
+      <c r="K899" t="n">
+        <v>20</v>
+      </c>
+      <c r="L899" t="b">
+        <v>0</v>
+      </c>
+      <c r="M899" t="b">
+        <v>0</v>
+      </c>
+      <c r="N899" t="b">
+        <v>0</v>
+      </c>
+      <c r="O899" t="b">
+        <v>0</v>
+      </c>
+      <c r="P899" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q899" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" t="inlineStr">
+        <is>
+          <t>p12</t>
+        </is>
+      </c>
+      <c r="B900" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C900" t="inlineStr">
+        <is>
+          <t>tune</t>
+        </is>
+      </c>
+      <c r="D900" t="inlineStr">
+        <is>
+          <t>chatgpt</t>
+        </is>
+      </c>
+      <c r="E900" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="F900" t="n">
+        <v>4</v>
+      </c>
+      <c r="G900" t="n">
+        <v>4</v>
+      </c>
+      <c r="H900" t="n">
+        <v>4</v>
+      </c>
+      <c r="I900" t="n">
+        <v>4</v>
+      </c>
+      <c r="J900" t="n">
+        <v>4</v>
+      </c>
+      <c r="K900" t="n">
+        <v>20</v>
+      </c>
+      <c r="L900" t="b">
+        <v>0</v>
+      </c>
+      <c r="M900" t="b">
+        <v>0</v>
+      </c>
+      <c r="N900" t="b">
+        <v>0</v>
+      </c>
+      <c r="O900" t="b">
+        <v>0</v>
+      </c>
+      <c r="P900" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q900" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" t="inlineStr">
+        <is>
+          <t>p12</t>
+        </is>
+      </c>
+      <c r="B901" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C901" t="inlineStr">
+        <is>
+          <t>tune</t>
+        </is>
+      </c>
+      <c r="D901" t="inlineStr">
+        <is>
+          <t>chatgpt</t>
+        </is>
+      </c>
+      <c r="E901" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="F901" t="n">
+        <v>4</v>
+      </c>
+      <c r="G901" t="n">
+        <v>4</v>
+      </c>
+      <c r="H901" t="n">
+        <v>4</v>
+      </c>
+      <c r="I901" t="n">
+        <v>4</v>
+      </c>
+      <c r="J901" t="n">
+        <v>4</v>
+      </c>
+      <c r="K901" t="n">
+        <v>20</v>
+      </c>
+      <c r="L901" t="b">
+        <v>0</v>
+      </c>
+      <c r="M901" t="b">
+        <v>0</v>
+      </c>
+      <c r="N901" t="b">
+        <v>0</v>
+      </c>
+      <c r="O901" t="b">
+        <v>0</v>
+      </c>
+      <c r="P901" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q901" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" t="inlineStr">
+        <is>
+          <t>p12</t>
+        </is>
+      </c>
+      <c r="B902" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C902" t="inlineStr">
+        <is>
+          <t>tune</t>
+        </is>
+      </c>
+      <c r="D902" t="inlineStr">
+        <is>
+          <t>chatgpt</t>
+        </is>
+      </c>
+      <c r="E902" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="F902" t="n">
+        <v>4</v>
+      </c>
+      <c r="G902" t="n">
+        <v>4</v>
+      </c>
+      <c r="H902" t="n">
+        <v>4</v>
+      </c>
+      <c r="I902" t="n">
+        <v>4</v>
+      </c>
+      <c r="J902" t="n">
+        <v>4</v>
+      </c>
+      <c r="K902" t="n">
+        <v>20</v>
+      </c>
+      <c r="L902" t="b">
+        <v>0</v>
+      </c>
+      <c r="M902" t="b">
+        <v>0</v>
+      </c>
+      <c r="N902" t="b">
+        <v>0</v>
+      </c>
+      <c r="O902" t="b">
+        <v>0</v>
+      </c>
+      <c r="P902" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q902" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" t="inlineStr">
+        <is>
+          <t>p12</t>
+        </is>
+      </c>
+      <c r="B903" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C903" t="inlineStr">
+        <is>
+          <t>tune</t>
+        </is>
+      </c>
+      <c r="D903" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="E903" t="inlineStr">
+        <is>
+          <t>chatgpt</t>
+        </is>
+      </c>
+      <c r="F903" t="n">
+        <v>4</v>
+      </c>
+      <c r="G903" t="n">
+        <v>3</v>
+      </c>
+      <c r="H903" t="n">
+        <v>4</v>
+      </c>
+      <c r="I903" t="n">
+        <v>4</v>
+      </c>
+      <c r="J903" t="n">
+        <v>3</v>
+      </c>
+      <c r="K903" t="n">
+        <v>18</v>
+      </c>
+      <c r="L903" t="b">
+        <v>0</v>
+      </c>
+      <c r="M903" t="b">
+        <v>0</v>
+      </c>
+      <c r="N903" t="b">
+        <v>0</v>
+      </c>
+      <c r="O903" t="b">
+        <v>0</v>
+      </c>
+      <c r="P903" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q903" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" t="inlineStr">
+        <is>
+          <t>p12</t>
+        </is>
+      </c>
+      <c r="B904" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C904" t="inlineStr">
+        <is>
+          <t>tune</t>
+        </is>
+      </c>
+      <c r="D904" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="E904" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="F904" t="n">
+        <v>4</v>
+      </c>
+      <c r="G904" t="n">
+        <v>4</v>
+      </c>
+      <c r="H904" t="n">
+        <v>4</v>
+      </c>
+      <c r="I904" t="n">
+        <v>4</v>
+      </c>
+      <c r="J904" t="n">
+        <v>4</v>
+      </c>
+      <c r="K904" t="n">
+        <v>20</v>
+      </c>
+      <c r="L904" t="b">
+        <v>0</v>
+      </c>
+      <c r="M904" t="b">
+        <v>0</v>
+      </c>
+      <c r="N904" t="b">
+        <v>0</v>
+      </c>
+      <c r="O904" t="b">
+        <v>0</v>
+      </c>
+      <c r="P904" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q904" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" t="inlineStr">
+        <is>
+          <t>p12</t>
+        </is>
+      </c>
+      <c r="B905" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C905" t="inlineStr">
+        <is>
+          <t>tune</t>
+        </is>
+      </c>
+      <c r="D905" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="E905" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="F905" t="n">
+        <v>4</v>
+      </c>
+      <c r="G905" t="n">
+        <v>4</v>
+      </c>
+      <c r="H905" t="n">
+        <v>4</v>
+      </c>
+      <c r="I905" t="n">
+        <v>4</v>
+      </c>
+      <c r="J905" t="n">
+        <v>4</v>
+      </c>
+      <c r="K905" t="n">
+        <v>20</v>
+      </c>
+      <c r="L905" t="b">
+        <v>0</v>
+      </c>
+      <c r="M905" t="b">
+        <v>0</v>
+      </c>
+      <c r="N905" t="b">
+        <v>0</v>
+      </c>
+      <c r="O905" t="b">
+        <v>0</v>
+      </c>
+      <c r="P905" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q905" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" t="inlineStr">
+        <is>
+          <t>p12</t>
+        </is>
+      </c>
+      <c r="B906" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C906" t="inlineStr">
+        <is>
+          <t>tune</t>
+        </is>
+      </c>
+      <c r="D906" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="E906" t="inlineStr">
+        <is>
+          <t>chatgpt</t>
+        </is>
+      </c>
+      <c r="F906" t="n">
+        <v>4</v>
+      </c>
+      <c r="G906" t="n">
+        <v>3</v>
+      </c>
+      <c r="H906" t="n">
+        <v>4</v>
+      </c>
+      <c r="I906" t="n">
+        <v>4</v>
+      </c>
+      <c r="J906" t="n">
+        <v>3</v>
+      </c>
+      <c r="K906" t="n">
+        <v>18</v>
+      </c>
+      <c r="L906" t="b">
+        <v>0</v>
+      </c>
+      <c r="M906" t="b">
+        <v>0</v>
+      </c>
+      <c r="N906" t="b">
+        <v>0</v>
+      </c>
+      <c r="O906" t="b">
+        <v>0</v>
+      </c>
+      <c r="P906" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q906" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" t="inlineStr">
+        <is>
+          <t>p12</t>
+        </is>
+      </c>
+      <c r="B907" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C907" t="inlineStr">
+        <is>
+          <t>tune</t>
+        </is>
+      </c>
+      <c r="D907" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="E907" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="F907" t="n">
+        <v>4</v>
+      </c>
+      <c r="G907" t="n">
+        <v>3</v>
+      </c>
+      <c r="H907" t="n">
+        <v>4</v>
+      </c>
+      <c r="I907" t="n">
+        <v>4</v>
+      </c>
+      <c r="J907" t="n">
+        <v>3</v>
+      </c>
+      <c r="K907" t="n">
+        <v>18</v>
+      </c>
+      <c r="L907" t="b">
+        <v>0</v>
+      </c>
+      <c r="M907" t="b">
+        <v>0</v>
+      </c>
+      <c r="N907" t="b">
+        <v>0</v>
+      </c>
+      <c r="O907" t="b">
+        <v>0</v>
+      </c>
+      <c r="P907" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q907" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" t="inlineStr">
+        <is>
+          <t>p12</t>
+        </is>
+      </c>
+      <c r="B908" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C908" t="inlineStr">
+        <is>
+          <t>tune</t>
+        </is>
+      </c>
+      <c r="D908" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="E908" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="F908" t="n">
+        <v>4</v>
+      </c>
+      <c r="G908" t="n">
+        <v>4</v>
+      </c>
+      <c r="H908" t="n">
+        <v>4</v>
+      </c>
+      <c r="I908" t="n">
+        <v>4</v>
+      </c>
+      <c r="J908" t="n">
+        <v>4</v>
+      </c>
+      <c r="K908" t="n">
+        <v>20</v>
+      </c>
+      <c r="L908" t="b">
+        <v>0</v>
+      </c>
+      <c r="M908" t="b">
+        <v>0</v>
+      </c>
+      <c r="N908" t="b">
+        <v>0</v>
+      </c>
+      <c r="O908" t="b">
+        <v>0</v>
+      </c>
+      <c r="P908" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q908" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" t="inlineStr">
+        <is>
+          <t>p12</t>
+        </is>
+      </c>
+      <c r="B909" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C909" t="inlineStr">
+        <is>
+          <t>tune</t>
+        </is>
+      </c>
+      <c r="D909" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="E909" t="inlineStr">
+        <is>
+          <t>chatgpt</t>
+        </is>
+      </c>
+      <c r="F909" t="n">
+        <v>4</v>
+      </c>
+      <c r="G909" t="n">
+        <v>4</v>
+      </c>
+      <c r="H909" t="n">
+        <v>4</v>
+      </c>
+      <c r="I909" t="n">
+        <v>4</v>
+      </c>
+      <c r="J909" t="n">
+        <v>4</v>
+      </c>
+      <c r="K909" t="n">
+        <v>20</v>
+      </c>
+      <c r="L909" t="b">
+        <v>0</v>
+      </c>
+      <c r="M909" t="b">
+        <v>0</v>
+      </c>
+      <c r="N909" t="b">
+        <v>0</v>
+      </c>
+      <c r="O909" t="b">
+        <v>0</v>
+      </c>
+      <c r="P909" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q909" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" t="inlineStr">
+        <is>
+          <t>p12</t>
+        </is>
+      </c>
+      <c r="B910" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C910" t="inlineStr">
+        <is>
+          <t>tune</t>
+        </is>
+      </c>
+      <c r="D910" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="E910" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="F910" t="n">
+        <v>4</v>
+      </c>
+      <c r="G910" t="n">
+        <v>4</v>
+      </c>
+      <c r="H910" t="n">
+        <v>4</v>
+      </c>
+      <c r="I910" t="n">
+        <v>4</v>
+      </c>
+      <c r="J910" t="n">
+        <v>4</v>
+      </c>
+      <c r="K910" t="n">
+        <v>20</v>
+      </c>
+      <c r="L910" t="b">
+        <v>0</v>
+      </c>
+      <c r="M910" t="b">
+        <v>0</v>
+      </c>
+      <c r="N910" t="b">
+        <v>0</v>
+      </c>
+      <c r="O910" t="b">
+        <v>0</v>
+      </c>
+      <c r="P910" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q910" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" t="inlineStr">
+        <is>
+          <t>p12</t>
+        </is>
+      </c>
+      <c r="B911" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C911" t="inlineStr">
+        <is>
+          <t>tune</t>
+        </is>
+      </c>
+      <c r="D911" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="E911" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="F911" t="n">
+        <v>4</v>
+      </c>
+      <c r="G911" t="n">
+        <v>4</v>
+      </c>
+      <c r="H911" t="n">
+        <v>4</v>
+      </c>
+      <c r="I911" t="n">
+        <v>4</v>
+      </c>
+      <c r="J911" t="n">
+        <v>4</v>
+      </c>
+      <c r="K911" t="n">
+        <v>20</v>
+      </c>
+      <c r="L911" t="b">
+        <v>0</v>
+      </c>
+      <c r="M911" t="b">
+        <v>0</v>
+      </c>
+      <c r="N911" t="b">
+        <v>0</v>
+      </c>
+      <c r="O911" t="b">
+        <v>0</v>
+      </c>
+      <c r="P911" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q911" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" t="inlineStr">
+        <is>
+          <t>p12</t>
+        </is>
+      </c>
+      <c r="B912" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C912" t="inlineStr">
+        <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="D912" t="inlineStr">
+        <is>
+          <t>chatgpt</t>
+        </is>
+      </c>
+      <c r="E912" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="F912" t="n">
+        <v>4</v>
+      </c>
+      <c r="G912" t="n">
+        <v>4</v>
+      </c>
+      <c r="H912" t="n">
+        <v>3</v>
+      </c>
+      <c r="I912" t="n">
+        <v>4</v>
+      </c>
+      <c r="J912" t="n">
+        <v>4</v>
+      </c>
+      <c r="K912" t="n">
+        <v>19</v>
+      </c>
+      <c r="L912" t="b">
+        <v>0</v>
+      </c>
+      <c r="M912" t="b">
+        <v>0</v>
+      </c>
+      <c r="N912" t="b">
+        <v>0</v>
+      </c>
+      <c r="O912" t="b">
+        <v>0</v>
+      </c>
+      <c r="P912" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q912" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" t="inlineStr">
+        <is>
+          <t>p12</t>
+        </is>
+      </c>
+      <c r="B913" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C913" t="inlineStr">
+        <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="D913" t="inlineStr">
+        <is>
+          <t>chatgpt</t>
+        </is>
+      </c>
+      <c r="E913" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="F913" t="n">
+        <v>4</v>
+      </c>
+      <c r="G913" t="n">
+        <v>4</v>
+      </c>
+      <c r="H913" t="n">
+        <v>4</v>
+      </c>
+      <c r="I913" t="n">
+        <v>4</v>
+      </c>
+      <c r="J913" t="n">
+        <v>4</v>
+      </c>
+      <c r="K913" t="n">
+        <v>20</v>
+      </c>
+      <c r="L913" t="b">
+        <v>0</v>
+      </c>
+      <c r="M913" t="b">
+        <v>0</v>
+      </c>
+      <c r="N913" t="b">
+        <v>0</v>
+      </c>
+      <c r="O913" t="b">
+        <v>0</v>
+      </c>
+      <c r="P913" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q913" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" t="inlineStr">
+        <is>
+          <t>p12</t>
+        </is>
+      </c>
+      <c r="B914" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C914" t="inlineStr">
+        <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="D914" t="inlineStr">
+        <is>
+          <t>chatgpt</t>
+        </is>
+      </c>
+      <c r="E914" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="F914" t="n">
+        <v>4</v>
+      </c>
+      <c r="G914" t="n">
+        <v>4</v>
+      </c>
+      <c r="H914" t="n">
+        <v>4</v>
+      </c>
+      <c r="I914" t="n">
+        <v>4</v>
+      </c>
+      <c r="J914" t="n">
+        <v>4</v>
+      </c>
+      <c r="K914" t="n">
+        <v>20</v>
+      </c>
+      <c r="L914" t="b">
+        <v>0</v>
+      </c>
+      <c r="M914" t="b">
+        <v>0</v>
+      </c>
+      <c r="N914" t="b">
+        <v>0</v>
+      </c>
+      <c r="O914" t="b">
+        <v>0</v>
+      </c>
+      <c r="P914" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q914" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" t="inlineStr">
+        <is>
+          <t>p12</t>
+        </is>
+      </c>
+      <c r="B915" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C915" t="inlineStr">
+        <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="D915" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="E915" t="inlineStr">
+        <is>
+          <t>chatgpt</t>
+        </is>
+      </c>
+      <c r="F915" t="n">
+        <v>4</v>
+      </c>
+      <c r="G915" t="n">
+        <v>3</v>
+      </c>
+      <c r="H915" t="n">
+        <v>3</v>
+      </c>
+      <c r="I915" t="n">
+        <v>3</v>
+      </c>
+      <c r="J915" t="n">
+        <v>2</v>
+      </c>
+      <c r="K915" t="n">
+        <v>15</v>
+      </c>
+      <c r="L915" t="b">
+        <v>0</v>
+      </c>
+      <c r="M915" t="b">
+        <v>0</v>
+      </c>
+      <c r="N915" t="b">
+        <v>0</v>
+      </c>
+      <c r="O915" t="b">
+        <v>0</v>
+      </c>
+      <c r="P915" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q915" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" t="inlineStr">
+        <is>
+          <t>p12</t>
+        </is>
+      </c>
+      <c r="B916" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C916" t="inlineStr">
+        <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="D916" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="E916" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="F916" t="n">
+        <v>4</v>
+      </c>
+      <c r="G916" t="n">
+        <v>3</v>
+      </c>
+      <c r="H916" t="n">
+        <v>3</v>
+      </c>
+      <c r="I916" t="n">
+        <v>4</v>
+      </c>
+      <c r="J916" t="n">
+        <v>3</v>
+      </c>
+      <c r="K916" t="n">
+        <v>17</v>
+      </c>
+      <c r="L916" t="b">
+        <v>0</v>
+      </c>
+      <c r="M916" t="b">
+        <v>0</v>
+      </c>
+      <c r="N916" t="b">
+        <v>0</v>
+      </c>
+      <c r="O916" t="b">
+        <v>0</v>
+      </c>
+      <c r="P916" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q916" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" t="inlineStr">
+        <is>
+          <t>p12</t>
+        </is>
+      </c>
+      <c r="B917" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C917" t="inlineStr">
+        <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="D917" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="E917" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="F917" t="n">
+        <v>4</v>
+      </c>
+      <c r="G917" t="n">
+        <v>4</v>
+      </c>
+      <c r="H917" t="n">
+        <v>4</v>
+      </c>
+      <c r="I917" t="n">
+        <v>4</v>
+      </c>
+      <c r="J917" t="n">
+        <v>3</v>
+      </c>
+      <c r="K917" t="n">
+        <v>19</v>
+      </c>
+      <c r="L917" t="b">
+        <v>0</v>
+      </c>
+      <c r="M917" t="b">
+        <v>0</v>
+      </c>
+      <c r="N917" t="b">
+        <v>0</v>
+      </c>
+      <c r="O917" t="b">
+        <v>0</v>
+      </c>
+      <c r="P917" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q917" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" t="inlineStr">
+        <is>
+          <t>p12</t>
+        </is>
+      </c>
+      <c r="B918" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C918" t="inlineStr">
+        <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="D918" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="E918" t="inlineStr">
+        <is>
+          <t>chatgpt</t>
+        </is>
+      </c>
+      <c r="F918" t="n">
+        <v>4</v>
+      </c>
+      <c r="G918" t="n">
+        <v>3</v>
+      </c>
+      <c r="H918" t="n">
+        <v>3</v>
+      </c>
+      <c r="I918" t="n">
+        <v>3</v>
+      </c>
+      <c r="J918" t="n">
+        <v>3</v>
+      </c>
+      <c r="K918" t="n">
+        <v>16</v>
+      </c>
+      <c r="L918" t="b">
+        <v>0</v>
+      </c>
+      <c r="M918" t="b">
+        <v>0</v>
+      </c>
+      <c r="N918" t="b">
+        <v>0</v>
+      </c>
+      <c r="O918" t="b">
+        <v>0</v>
+      </c>
+      <c r="P918" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q918" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" t="inlineStr">
+        <is>
+          <t>p12</t>
+        </is>
+      </c>
+      <c r="B919" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C919" t="inlineStr">
+        <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="D919" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="E919" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="F919" t="n">
+        <v>4</v>
+      </c>
+      <c r="G919" t="n">
+        <v>3</v>
+      </c>
+      <c r="H919" t="n">
+        <v>3</v>
+      </c>
+      <c r="I919" t="n">
+        <v>4</v>
+      </c>
+      <c r="J919" t="n">
+        <v>3</v>
+      </c>
+      <c r="K919" t="n">
+        <v>17</v>
+      </c>
+      <c r="L919" t="b">
+        <v>0</v>
+      </c>
+      <c r="M919" t="b">
+        <v>0</v>
+      </c>
+      <c r="N919" t="b">
+        <v>0</v>
+      </c>
+      <c r="O919" t="b">
+        <v>0</v>
+      </c>
+      <c r="P919" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q919" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" t="inlineStr">
+        <is>
+          <t>p12</t>
+        </is>
+      </c>
+      <c r="B920" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C920" t="inlineStr">
+        <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="D920" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="E920" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="F920" t="n">
+        <v>4</v>
+      </c>
+      <c r="G920" t="n">
+        <v>4</v>
+      </c>
+      <c r="H920" t="n">
+        <v>3</v>
+      </c>
+      <c r="I920" t="n">
+        <v>4</v>
+      </c>
+      <c r="J920" t="n">
+        <v>4</v>
+      </c>
+      <c r="K920" t="n">
+        <v>19</v>
+      </c>
+      <c r="L920" t="b">
+        <v>0</v>
+      </c>
+      <c r="M920" t="b">
+        <v>0</v>
+      </c>
+      <c r="N920" t="b">
+        <v>0</v>
+      </c>
+      <c r="O920" t="b">
+        <v>0</v>
+      </c>
+      <c r="P920" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q920" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" t="inlineStr">
+        <is>
+          <t>p12</t>
+        </is>
+      </c>
+      <c r="B921" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C921" t="inlineStr">
+        <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="D921" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="E921" t="inlineStr">
+        <is>
+          <t>chatgpt</t>
+        </is>
+      </c>
+      <c r="F921" t="n">
+        <v>4</v>
+      </c>
+      <c r="G921" t="n">
+        <v>3</v>
+      </c>
+      <c r="H921" t="n">
+        <v>3</v>
+      </c>
+      <c r="I921" t="n">
+        <v>3</v>
+      </c>
+      <c r="J921" t="n">
+        <v>3</v>
+      </c>
+      <c r="K921" t="n">
+        <v>16</v>
+      </c>
+      <c r="L921" t="b">
+        <v>0</v>
+      </c>
+      <c r="M921" t="b">
+        <v>0</v>
+      </c>
+      <c r="N921" t="b">
+        <v>0</v>
+      </c>
+      <c r="O921" t="b">
+        <v>0</v>
+      </c>
+      <c r="P921" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q921" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" t="inlineStr">
+        <is>
+          <t>p12</t>
+        </is>
+      </c>
+      <c r="B922" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C922" t="inlineStr">
+        <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="D922" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="E922" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="F922" t="n">
+        <v>4</v>
+      </c>
+      <c r="G922" t="n">
+        <v>4</v>
+      </c>
+      <c r="H922" t="n">
+        <v>3</v>
+      </c>
+      <c r="I922" t="n">
+        <v>3</v>
+      </c>
+      <c r="J922" t="n">
+        <v>3</v>
+      </c>
+      <c r="K922" t="n">
+        <v>17</v>
+      </c>
+      <c r="L922" t="b">
+        <v>0</v>
+      </c>
+      <c r="M922" t="b">
+        <v>0</v>
+      </c>
+      <c r="N922" t="b">
+        <v>0</v>
+      </c>
+      <c r="O922" t="b">
+        <v>0</v>
+      </c>
+      <c r="P922" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q922" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" t="inlineStr">
+        <is>
+          <t>p12</t>
+        </is>
+      </c>
+      <c r="B923" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C923" t="inlineStr">
+        <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="D923" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="E923" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="F923" t="n">
+        <v>4</v>
+      </c>
+      <c r="G923" t="n">
+        <v>4</v>
+      </c>
+      <c r="H923" t="n">
+        <v>4</v>
+      </c>
+      <c r="I923" t="n">
+        <v>4</v>
+      </c>
+      <c r="J923" t="n">
+        <v>4</v>
+      </c>
+      <c r="K923" t="n">
+        <v>20</v>
+      </c>
+      <c r="L923" t="b">
+        <v>0</v>
+      </c>
+      <c r="M923" t="b">
+        <v>0</v>
+      </c>
+      <c r="N923" t="b">
+        <v>0</v>
+      </c>
+      <c r="O923" t="b">
+        <v>0</v>
+      </c>
+      <c r="P923" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q923" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" t="inlineStr">
+        <is>
+          <t>p12</t>
+        </is>
+      </c>
+      <c r="B924" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C924" t="inlineStr">
+        <is>
+          <t>tune</t>
+        </is>
+      </c>
+      <c r="D924" t="inlineStr">
+        <is>
+          <t>chatgpt</t>
+        </is>
+      </c>
+      <c r="E924" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="F924" t="n">
+        <v>4</v>
+      </c>
+      <c r="G924" t="n">
+        <v>4</v>
+      </c>
+      <c r="H924" t="n">
+        <v>4</v>
+      </c>
+      <c r="I924" t="n">
+        <v>4</v>
+      </c>
+      <c r="J924" t="n">
+        <v>4</v>
+      </c>
+      <c r="K924" t="n">
+        <v>20</v>
+      </c>
+      <c r="L924" t="b">
+        <v>0</v>
+      </c>
+      <c r="M924" t="b">
+        <v>0</v>
+      </c>
+      <c r="N924" t="b">
+        <v>0</v>
+      </c>
+      <c r="O924" t="b">
+        <v>0</v>
+      </c>
+      <c r="P924" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q924" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" t="inlineStr">
+        <is>
+          <t>p12</t>
+        </is>
+      </c>
+      <c r="B925" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C925" t="inlineStr">
+        <is>
+          <t>tune</t>
+        </is>
+      </c>
+      <c r="D925" t="inlineStr">
+        <is>
+          <t>chatgpt</t>
+        </is>
+      </c>
+      <c r="E925" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="F925" t="n">
+        <v>4</v>
+      </c>
+      <c r="G925" t="n">
+        <v>4</v>
+      </c>
+      <c r="H925" t="n">
+        <v>4</v>
+      </c>
+      <c r="I925" t="n">
+        <v>4</v>
+      </c>
+      <c r="J925" t="n">
+        <v>4</v>
+      </c>
+      <c r="K925" t="n">
+        <v>20</v>
+      </c>
+      <c r="L925" t="b">
+        <v>0</v>
+      </c>
+      <c r="M925" t="b">
+        <v>0</v>
+      </c>
+      <c r="N925" t="b">
+        <v>0</v>
+      </c>
+      <c r="O925" t="b">
+        <v>0</v>
+      </c>
+      <c r="P925" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q925" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" t="inlineStr">
+        <is>
+          <t>p12</t>
+        </is>
+      </c>
+      <c r="B926" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C926" t="inlineStr">
+        <is>
+          <t>tune</t>
+        </is>
+      </c>
+      <c r="D926" t="inlineStr">
+        <is>
+          <t>chatgpt</t>
+        </is>
+      </c>
+      <c r="E926" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="F926" t="n">
+        <v>4</v>
+      </c>
+      <c r="G926" t="n">
+        <v>4</v>
+      </c>
+      <c r="H926" t="n">
+        <v>4</v>
+      </c>
+      <c r="I926" t="n">
+        <v>4</v>
+      </c>
+      <c r="J926" t="n">
+        <v>4</v>
+      </c>
+      <c r="K926" t="n">
+        <v>20</v>
+      </c>
+      <c r="L926" t="b">
+        <v>0</v>
+      </c>
+      <c r="M926" t="b">
+        <v>0</v>
+      </c>
+      <c r="N926" t="b">
+        <v>0</v>
+      </c>
+      <c r="O926" t="b">
+        <v>0</v>
+      </c>
+      <c r="P926" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q926" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" t="inlineStr">
+        <is>
+          <t>p12</t>
+        </is>
+      </c>
+      <c r="B927" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C927" t="inlineStr">
+        <is>
+          <t>tune</t>
+        </is>
+      </c>
+      <c r="D927" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="E927" t="inlineStr">
+        <is>
+          <t>chatgpt</t>
+        </is>
+      </c>
+      <c r="F927" t="n">
+        <v>4</v>
+      </c>
+      <c r="G927" t="n">
+        <v>4</v>
+      </c>
+      <c r="H927" t="n">
+        <v>4</v>
+      </c>
+      <c r="I927" t="n">
+        <v>4</v>
+      </c>
+      <c r="J927" t="n">
+        <v>4</v>
+      </c>
+      <c r="K927" t="n">
+        <v>20</v>
+      </c>
+      <c r="L927" t="b">
+        <v>0</v>
+      </c>
+      <c r="M927" t="b">
+        <v>0</v>
+      </c>
+      <c r="N927" t="b">
+        <v>0</v>
+      </c>
+      <c r="O927" t="b">
+        <v>0</v>
+      </c>
+      <c r="P927" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q927" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" t="inlineStr">
+        <is>
+          <t>p12</t>
+        </is>
+      </c>
+      <c r="B928" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C928" t="inlineStr">
+        <is>
+          <t>tune</t>
+        </is>
+      </c>
+      <c r="D928" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="E928" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="F928" t="n">
+        <v>4</v>
+      </c>
+      <c r="G928" t="n">
+        <v>4</v>
+      </c>
+      <c r="H928" t="n">
+        <v>4</v>
+      </c>
+      <c r="I928" t="n">
+        <v>4</v>
+      </c>
+      <c r="J928" t="n">
+        <v>4</v>
+      </c>
+      <c r="K928" t="n">
+        <v>20</v>
+      </c>
+      <c r="L928" t="b">
+        <v>0</v>
+      </c>
+      <c r="M928" t="b">
+        <v>0</v>
+      </c>
+      <c r="N928" t="b">
+        <v>0</v>
+      </c>
+      <c r="O928" t="b">
+        <v>0</v>
+      </c>
+      <c r="P928" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q928" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" t="inlineStr">
+        <is>
+          <t>p12</t>
+        </is>
+      </c>
+      <c r="B929" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C929" t="inlineStr">
+        <is>
+          <t>tune</t>
+        </is>
+      </c>
+      <c r="D929" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="E929" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="F929" t="n">
+        <v>4</v>
+      </c>
+      <c r="G929" t="n">
+        <v>4</v>
+      </c>
+      <c r="H929" t="n">
+        <v>4</v>
+      </c>
+      <c r="I929" t="n">
+        <v>4</v>
+      </c>
+      <c r="J929" t="n">
+        <v>4</v>
+      </c>
+      <c r="K929" t="n">
+        <v>20</v>
+      </c>
+      <c r="L929" t="b">
+        <v>0</v>
+      </c>
+      <c r="M929" t="b">
+        <v>0</v>
+      </c>
+      <c r="N929" t="b">
+        <v>0</v>
+      </c>
+      <c r="O929" t="b">
+        <v>0</v>
+      </c>
+      <c r="P929" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q929" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" t="inlineStr">
+        <is>
+          <t>p12</t>
+        </is>
+      </c>
+      <c r="B930" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C930" t="inlineStr">
+        <is>
+          <t>tune</t>
+        </is>
+      </c>
+      <c r="D930" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="E930" t="inlineStr">
+        <is>
+          <t>chatgpt</t>
+        </is>
+      </c>
+      <c r="F930" t="n">
+        <v>4</v>
+      </c>
+      <c r="G930" t="n">
+        <v>3</v>
+      </c>
+      <c r="H930" t="n">
+        <v>3</v>
+      </c>
+      <c r="I930" t="n">
+        <v>4</v>
+      </c>
+      <c r="J930" t="n">
+        <v>3</v>
+      </c>
+      <c r="K930" t="n">
+        <v>17</v>
+      </c>
+      <c r="L930" t="b">
+        <v>0</v>
+      </c>
+      <c r="M930" t="b">
+        <v>0</v>
+      </c>
+      <c r="N930" t="b">
+        <v>0</v>
+      </c>
+      <c r="O930" t="b">
+        <v>0</v>
+      </c>
+      <c r="P930" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q930" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" t="inlineStr">
+        <is>
+          <t>p12</t>
+        </is>
+      </c>
+      <c r="B931" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C931" t="inlineStr">
+        <is>
+          <t>tune</t>
+        </is>
+      </c>
+      <c r="D931" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="E931" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="F931" t="n">
+        <v>4</v>
+      </c>
+      <c r="G931" t="n">
+        <v>4</v>
+      </c>
+      <c r="H931" t="n">
+        <v>4</v>
+      </c>
+      <c r="I931" t="n">
+        <v>3</v>
+      </c>
+      <c r="J931" t="n">
+        <v>4</v>
+      </c>
+      <c r="K931" t="n">
+        <v>19</v>
+      </c>
+      <c r="L931" t="b">
+        <v>0</v>
+      </c>
+      <c r="M931" t="b">
+        <v>0</v>
+      </c>
+      <c r="N931" t="b">
+        <v>0</v>
+      </c>
+      <c r="O931" t="b">
+        <v>0</v>
+      </c>
+      <c r="P931" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q931" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" t="inlineStr">
+        <is>
+          <t>p12</t>
+        </is>
+      </c>
+      <c r="B932" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C932" t="inlineStr">
+        <is>
+          <t>tune</t>
+        </is>
+      </c>
+      <c r="D932" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="E932" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="F932" t="n">
+        <v>4</v>
+      </c>
+      <c r="G932" t="n">
+        <v>4</v>
+      </c>
+      <c r="H932" t="n">
+        <v>4</v>
+      </c>
+      <c r="I932" t="n">
+        <v>4</v>
+      </c>
+      <c r="J932" t="n">
+        <v>4</v>
+      </c>
+      <c r="K932" t="n">
+        <v>20</v>
+      </c>
+      <c r="L932" t="b">
+        <v>0</v>
+      </c>
+      <c r="M932" t="b">
+        <v>0</v>
+      </c>
+      <c r="N932" t="b">
+        <v>0</v>
+      </c>
+      <c r="O932" t="b">
+        <v>0</v>
+      </c>
+      <c r="P932" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q932" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" t="inlineStr">
+        <is>
+          <t>p12</t>
+        </is>
+      </c>
+      <c r="B933" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C933" t="inlineStr">
+        <is>
+          <t>tune</t>
+        </is>
+      </c>
+      <c r="D933" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="E933" t="inlineStr">
+        <is>
+          <t>chatgpt</t>
+        </is>
+      </c>
+      <c r="F933" t="n">
+        <v>4</v>
+      </c>
+      <c r="G933" t="n">
+        <v>4</v>
+      </c>
+      <c r="H933" t="n">
+        <v>4</v>
+      </c>
+      <c r="I933" t="n">
+        <v>3</v>
+      </c>
+      <c r="J933" t="n">
+        <v>4</v>
+      </c>
+      <c r="K933" t="n">
+        <v>19</v>
+      </c>
+      <c r="L933" t="b">
+        <v>0</v>
+      </c>
+      <c r="M933" t="b">
+        <v>0</v>
+      </c>
+      <c r="N933" t="b">
+        <v>0</v>
+      </c>
+      <c r="O933" t="b">
+        <v>0</v>
+      </c>
+      <c r="P933" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q933" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" t="inlineStr">
+        <is>
+          <t>p12</t>
+        </is>
+      </c>
+      <c r="B934" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C934" t="inlineStr">
+        <is>
+          <t>tune</t>
+        </is>
+      </c>
+      <c r="D934" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="E934" t="inlineStr">
+        <is>
+          <t>claude</t>
+        </is>
+      </c>
+      <c r="F934" t="n">
+        <v>4</v>
+      </c>
+      <c r="G934" t="n">
+        <v>4</v>
+      </c>
+      <c r="H934" t="n">
+        <v>4</v>
+      </c>
+      <c r="I934" t="n">
+        <v>4</v>
+      </c>
+      <c r="J934" t="n">
+        <v>4</v>
+      </c>
+      <c r="K934" t="n">
+        <v>20</v>
+      </c>
+      <c r="L934" t="b">
+        <v>0</v>
+      </c>
+      <c r="M934" t="b">
+        <v>0</v>
+      </c>
+      <c r="N934" t="b">
+        <v>0</v>
+      </c>
+      <c r="O934" t="b">
+        <v>0</v>
+      </c>
+      <c r="P934" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q934" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" t="inlineStr">
+        <is>
+          <t>p12</t>
+        </is>
+      </c>
+      <c r="B935" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C935" t="inlineStr">
+        <is>
+          <t>tune</t>
+        </is>
+      </c>
+      <c r="D935" t="inlineStr">
+        <is>
+          <t>grok</t>
+        </is>
+      </c>
+      <c r="E935" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="F935" t="n">
+        <v>4</v>
+      </c>
+      <c r="G935" t="n">
+        <v>4</v>
+      </c>
+      <c r="H935" t="n">
+        <v>4</v>
+      </c>
+      <c r="I935" t="n">
+        <v>4</v>
+      </c>
+      <c r="J935" t="n">
+        <v>4</v>
+      </c>
+      <c r="K935" t="n">
+        <v>20</v>
+      </c>
+      <c r="L935" t="b">
+        <v>0</v>
+      </c>
+      <c r="M935" t="b">
+        <v>0</v>
+      </c>
+      <c r="N935" t="b">
+        <v>0</v>
+      </c>
+      <c r="O935" t="b">
+        <v>0</v>
+      </c>
+      <c r="P935" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q935" t="b">
         <v>0</v>
       </c>
     </row>

--- a/src/scores_all.xlsx
+++ b/src/scores_all.xlsx
@@ -33428,22 +33428,22 @@
         </is>
       </c>
       <c r="F524" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G524" t="n">
         <v>3</v>
       </c>
       <c r="H524" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I524" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J524" t="n">
         <v>3</v>
       </c>
       <c r="K524" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L524" t="b">
         <v>0</v>
@@ -33620,19 +33620,19 @@
         <v>4</v>
       </c>
       <c r="G527" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H527" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I527" t="n">
         <v>4</v>
       </c>
       <c r="J527" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K527" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L527" t="b">
         <v>0</v>
@@ -33680,22 +33680,22 @@
         </is>
       </c>
       <c r="F528" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G528" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H528" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I528" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J528" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K528" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="L528" t="b">
         <v>0</v>
@@ -34754,19 +34754,19 @@
         <v>4</v>
       </c>
       <c r="G545" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H545" t="n">
         <v>4</v>
       </c>
       <c r="I545" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J545" t="n">
         <v>4</v>
       </c>
       <c r="K545" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L545" t="b">
         <v>0</v>
@@ -34943,19 +34943,19 @@
         <v>4</v>
       </c>
       <c r="G548" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H548" t="n">
         <v>4</v>
       </c>
       <c r="I548" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J548" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K548" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L548" t="b">
         <v>0</v>
@@ -35015,10 +35015,10 @@
         <v>4</v>
       </c>
       <c r="J549" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K549" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L549" t="b">
         <v>0</v>
@@ -35138,13 +35138,13 @@
         <v>4</v>
       </c>
       <c r="I551" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J551" t="n">
         <v>3</v>
       </c>
       <c r="K551" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L551" t="b">
         <v>0</v>
@@ -36464,10 +36464,10 @@
         <v>4</v>
       </c>
       <c r="J572" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K572" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L572" t="b">
         <v>0</v>
@@ -36527,10 +36527,10 @@
         <v>4</v>
       </c>
       <c r="J573" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K573" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L573" t="b">
         <v>0</v>
@@ -36647,16 +36647,16 @@
         <v>4</v>
       </c>
       <c r="H575" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I575" t="n">
         <v>4</v>
       </c>
       <c r="J575" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K575" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L575" t="b">
         <v>0</v>
@@ -36716,10 +36716,10 @@
         <v>4</v>
       </c>
       <c r="J576" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K576" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L576" t="b">
         <v>0</v>
@@ -37787,10 +37787,10 @@
         <v>4</v>
       </c>
       <c r="J593" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K593" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L593" t="b">
         <v>0</v>
@@ -37970,10 +37970,10 @@
         <v>3</v>
       </c>
       <c r="H596" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I596" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J596" t="n">
         <v>3</v>
@@ -38039,10 +38039,10 @@
         <v>4</v>
       </c>
       <c r="J597" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K597" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L597" t="b">
         <v>0</v>
@@ -38165,10 +38165,10 @@
         <v>4</v>
       </c>
       <c r="J599" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K599" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L599" t="b">
         <v>0</v>
@@ -38216,7 +38216,7 @@
         </is>
       </c>
       <c r="F600" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G600" t="n">
         <v>4</v>
@@ -38231,7 +38231,7 @@
         <v>3</v>
       </c>
       <c r="K600" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L600" t="b">
         <v>0</v>
@@ -39290,7 +39290,7 @@
         <v>4</v>
       </c>
       <c r="G617" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H617" t="n">
         <v>4</v>
@@ -39302,7 +39302,7 @@
         <v>4</v>
       </c>
       <c r="K617" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L617" t="b">
         <v>0</v>
@@ -39479,19 +39479,19 @@
         <v>4</v>
       </c>
       <c r="G620" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H620" t="n">
         <v>4</v>
       </c>
       <c r="I620" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J620" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K620" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L620" t="b">
         <v>0</v>
@@ -39551,10 +39551,10 @@
         <v>4</v>
       </c>
       <c r="J621" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K621" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L621" t="b">
         <v>0</v>
@@ -39668,19 +39668,19 @@
         <v>4</v>
       </c>
       <c r="G623" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H623" t="n">
         <v>4</v>
       </c>
       <c r="I623" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J623" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K623" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L623" t="b">
         <v>0</v>
@@ -39728,22 +39728,22 @@
         </is>
       </c>
       <c r="F624" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G624" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H624" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I624" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J624" t="n">
         <v>3</v>
       </c>
       <c r="K624" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L624" t="b">
         <v>0</v>
@@ -40613,19 +40613,19 @@
         <v>4</v>
       </c>
       <c r="G638" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H638" t="n">
         <v>4</v>
       </c>
       <c r="I638" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J638" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K638" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L638" t="b">
         <v>0</v>
@@ -40802,13 +40802,13 @@
         <v>4</v>
       </c>
       <c r="G641" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H641" t="n">
         <v>4</v>
       </c>
       <c r="I641" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J641" t="n">
         <v>4</v>
@@ -41054,7 +41054,7 @@
         <v>4</v>
       </c>
       <c r="G645" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H645" t="n">
         <v>4</v>
@@ -41063,7 +41063,7 @@
         <v>4</v>
       </c>
       <c r="J645" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K645" t="n">
         <v>19</v>
@@ -41186,13 +41186,13 @@
         <v>4</v>
       </c>
       <c r="I647" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J647" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K647" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L647" t="b">
         <v>0</v>
@@ -42323,10 +42323,10 @@
         <v>4</v>
       </c>
       <c r="J665" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K665" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L665" t="b">
         <v>0</v>
@@ -42503,7 +42503,7 @@
         <v>4</v>
       </c>
       <c r="G668" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H668" t="n">
         <v>4</v>
@@ -42515,7 +42515,7 @@
         <v>3</v>
       </c>
       <c r="K668" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L668" t="b">
         <v>0</v>
@@ -42575,10 +42575,10 @@
         <v>4</v>
       </c>
       <c r="J669" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K669" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L669" t="b">
         <v>0</v>
@@ -42701,10 +42701,10 @@
         <v>4</v>
       </c>
       <c r="J671" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K671" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L671" t="b">
         <v>0</v>
@@ -43637,7 +43637,7 @@
         <v>4</v>
       </c>
       <c r="G686" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H686" t="n">
         <v>4</v>
@@ -43649,7 +43649,7 @@
         <v>4</v>
       </c>
       <c r="K686" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L686" t="b">
         <v>0</v>
@@ -43826,7 +43826,7 @@
         <v>4</v>
       </c>
       <c r="G689" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H689" t="n">
         <v>4</v>
@@ -43835,10 +43835,10 @@
         <v>4</v>
       </c>
       <c r="J689" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K689" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L689" t="b">
         <v>0</v>
@@ -44024,10 +44024,10 @@
         <v>4</v>
       </c>
       <c r="J692" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K692" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L692" t="b">
         <v>0</v>
@@ -44087,10 +44087,10 @@
         <v>4</v>
       </c>
       <c r="J693" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K693" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L693" t="b">
         <v>0</v>
@@ -44213,10 +44213,10 @@
         <v>4</v>
       </c>
       <c r="J695" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K695" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L695" t="b">
         <v>0</v>
@@ -44273,13 +44273,13 @@
         <v>4</v>
       </c>
       <c r="I696" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J696" t="n">
         <v>4</v>
       </c>
       <c r="K696" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L696" t="b">
         <v>0</v>
@@ -45338,19 +45338,19 @@
         <v>4</v>
       </c>
       <c r="G713" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H713" t="n">
         <v>4</v>
       </c>
       <c r="I713" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J713" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K713" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L713" t="b">
         <v>0</v>
@@ -45530,13 +45530,13 @@
         <v>3</v>
       </c>
       <c r="H716" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I716" t="n">
         <v>4</v>
       </c>
       <c r="J716" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K716" t="n">
         <v>18</v>
@@ -45599,10 +45599,10 @@
         <v>4</v>
       </c>
       <c r="J717" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K717" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L717" t="b">
         <v>0</v>
@@ -45716,19 +45716,19 @@
         <v>4</v>
       </c>
       <c r="G719" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H719" t="n">
         <v>4</v>
       </c>
       <c r="I719" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J719" t="n">
         <v>4</v>
       </c>
       <c r="K719" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L719" t="b">
         <v>0</v>
@@ -45788,10 +45788,10 @@
         <v>4</v>
       </c>
       <c r="J720" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K720" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L720" t="b">
         <v>0</v>
@@ -46664,7 +46664,7 @@
         <v>4</v>
       </c>
       <c r="H734" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I734" t="n">
         <v>4</v>
@@ -46673,7 +46673,7 @@
         <v>4</v>
       </c>
       <c r="K734" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L734" t="b">
         <v>0</v>
@@ -46850,7 +46850,7 @@
         <v>4</v>
       </c>
       <c r="G737" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H737" t="n">
         <v>4</v>
@@ -46859,7 +46859,7 @@
         <v>4</v>
       </c>
       <c r="J737" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K737" t="n">
         <v>19</v>
@@ -47231,16 +47231,16 @@
         <v>4</v>
       </c>
       <c r="H743" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I743" t="n">
         <v>4</v>
       </c>
       <c r="J743" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K743" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L743" t="b">
         <v>0</v>
@@ -47297,13 +47297,13 @@
         <v>4</v>
       </c>
       <c r="I744" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J744" t="n">
         <v>4</v>
       </c>
       <c r="K744" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L744" t="b">
         <v>0</v>
@@ -48179,13 +48179,13 @@
         <v>4</v>
       </c>
       <c r="I758" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J758" t="n">
         <v>4</v>
       </c>
       <c r="K758" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L758" t="b">
         <v>0</v>
@@ -48362,13 +48362,13 @@
         <v>4</v>
       </c>
       <c r="G761" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H761" t="n">
         <v>4</v>
       </c>
       <c r="I761" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J761" t="n">
         <v>4</v>
@@ -48557,13 +48557,13 @@
         <v>4</v>
       </c>
       <c r="I764" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J764" t="n">
         <v>3</v>
       </c>
       <c r="K764" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L764" t="b">
         <v>0</v>
@@ -48617,7 +48617,7 @@
         <v>4</v>
       </c>
       <c r="H765" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I765" t="n">
         <v>4</v>
@@ -48626,7 +48626,7 @@
         <v>4</v>
       </c>
       <c r="K765" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L765" t="b">
         <v>0</v>
@@ -48746,13 +48746,13 @@
         <v>4</v>
       </c>
       <c r="I767" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J767" t="n">
         <v>4</v>
       </c>
       <c r="K767" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L767" t="b">
         <v>0</v>
@@ -48812,10 +48812,10 @@
         <v>4</v>
       </c>
       <c r="J768" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K768" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L768" t="b">
         <v>0</v>
@@ -49748,7 +49748,7 @@
         <v>4</v>
       </c>
       <c r="G783" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H783" t="n">
         <v>4</v>
@@ -49760,7 +49760,7 @@
         <v>4</v>
       </c>
       <c r="K783" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L783" t="b">
         <v>0</v>
@@ -49937,19 +49937,19 @@
         <v>4</v>
       </c>
       <c r="G786" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H786" t="n">
         <v>4</v>
       </c>
       <c r="I786" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J786" t="n">
         <v>3</v>
       </c>
       <c r="K786" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L786" t="b">
         <v>0</v>
@@ -50003,16 +50003,16 @@
         <v>3</v>
       </c>
       <c r="H787" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I787" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J787" t="n">
         <v>3</v>
       </c>
       <c r="K787" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L787" t="b">
         <v>0</v>
@@ -50129,16 +50129,16 @@
         <v>4</v>
       </c>
       <c r="H789" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I789" t="n">
         <v>4</v>
       </c>
       <c r="J789" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K789" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L789" t="b">
         <v>0</v>
@@ -51260,19 +51260,19 @@
         <v>4</v>
       </c>
       <c r="G807" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H807" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I807" t="n">
         <v>4</v>
       </c>
       <c r="J807" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K807" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L807" t="b">
         <v>0</v>
@@ -51455,13 +51455,13 @@
         <v>4</v>
       </c>
       <c r="I810" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J810" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K810" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L810" t="b">
         <v>0</v>
@@ -51512,19 +51512,19 @@
         <v>4</v>
       </c>
       <c r="G811" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H811" t="n">
         <v>4</v>
       </c>
       <c r="I811" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J811" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K811" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L811" t="b">
         <v>0</v>
@@ -52583,7 +52583,7 @@
         <v>4</v>
       </c>
       <c r="G828" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H828" t="n">
         <v>4</v>
@@ -52595,7 +52595,7 @@
         <v>4</v>
       </c>
       <c r="K828" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L828" t="b">
         <v>0</v>
@@ -52970,10 +52970,10 @@
         <v>4</v>
       </c>
       <c r="J834" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K834" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L834" t="b">
         <v>0</v>
@@ -54284,7 +54284,7 @@
         <v>4</v>
       </c>
       <c r="G855" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H855" t="n">
         <v>4</v>
@@ -54296,7 +54296,7 @@
         <v>4</v>
       </c>
       <c r="K855" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L855" t="b">
         <v>0</v>
@@ -54473,10 +54473,10 @@
         <v>4</v>
       </c>
       <c r="G858" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H858" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I858" t="n">
         <v>4</v>
@@ -54485,7 +54485,7 @@
         <v>4</v>
       </c>
       <c r="K858" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L858" t="b">
         <v>0</v>
@@ -54536,19 +54536,19 @@
         <v>4</v>
       </c>
       <c r="G859" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H859" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I859" t="n">
         <v>4</v>
       </c>
       <c r="J859" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K859" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L859" t="b">
         <v>0</v>
@@ -54662,7 +54662,7 @@
         <v>4</v>
       </c>
       <c r="G861" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H861" t="n">
         <v>4</v>
@@ -54671,10 +54671,10 @@
         <v>4</v>
       </c>
       <c r="J861" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K861" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L861" t="b">
         <v>0</v>
@@ -55796,7 +55796,7 @@
         <v>4</v>
       </c>
       <c r="G879" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H879" t="n">
         <v>4</v>
@@ -55808,7 +55808,7 @@
         <v>3</v>
       </c>
       <c r="K879" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L879" t="b">
         <v>0</v>
@@ -55985,13 +55985,13 @@
         <v>4</v>
       </c>
       <c r="G882" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H882" t="n">
         <v>4</v>
       </c>
       <c r="I882" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J882" t="n">
         <v>3</v>
@@ -56174,7 +56174,7 @@
         <v>4</v>
       </c>
       <c r="G885" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H885" t="n">
         <v>4</v>
@@ -56183,10 +56183,10 @@
         <v>4</v>
       </c>
       <c r="J885" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K885" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L885" t="b">
         <v>0</v>
@@ -57314,13 +57314,13 @@
         <v>4</v>
       </c>
       <c r="I903" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J903" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K903" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L903" t="b">
         <v>0</v>
@@ -57497,7 +57497,7 @@
         <v>4</v>
       </c>
       <c r="G906" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H906" t="n">
         <v>4</v>
@@ -57506,10 +57506,10 @@
         <v>4</v>
       </c>
       <c r="J906" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K906" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L906" t="b">
         <v>0</v>
@@ -57560,7 +57560,7 @@
         <v>4</v>
       </c>
       <c r="G907" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H907" t="n">
         <v>4</v>
@@ -57572,7 +57572,7 @@
         <v>3</v>
       </c>
       <c r="K907" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L907" t="b">
         <v>0</v>
@@ -57758,10 +57758,10 @@
         <v>4</v>
       </c>
       <c r="J910" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K910" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L910" t="b">
         <v>0</v>
@@ -58823,16 +58823,16 @@
         <v>4</v>
       </c>
       <c r="H927" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I927" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J927" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K927" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="L927" t="b">
         <v>0</v>
@@ -58892,13 +58892,13 @@
         <v>4</v>
       </c>
       <c r="J928" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K928" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="L928" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M928" t="b">
         <v>0</v>
@@ -58913,7 +58913,7 @@
         <v>0</v>
       </c>
       <c r="Q928" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="929">
@@ -58952,13 +58952,13 @@
         <v>4</v>
       </c>
       <c r="I929" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J929" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K929" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L929" t="b">
         <v>0</v>
@@ -59012,7 +59012,7 @@
         <v>3</v>
       </c>
       <c r="H930" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I930" t="n">
         <v>4</v>
@@ -59021,7 +59021,7 @@
         <v>3</v>
       </c>
       <c r="K930" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L930" t="b">
         <v>0</v>
@@ -59072,19 +59072,19 @@
         <v>4</v>
       </c>
       <c r="G931" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H931" t="n">
         <v>4</v>
       </c>
       <c r="I931" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J931" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K931" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L931" t="b">
         <v>0</v>
@@ -59204,10 +59204,10 @@
         <v>4</v>
       </c>
       <c r="I933" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J933" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K933" t="n">
         <v>19</v>
